--- a/research/traditional_assets/database/data/cyprus/cyprus_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_aerospace_defense.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09862662881175452</v>
+        <v>0.09854272052573983</v>
       </c>
       <c r="C2">
-        <v>992.6683553824688</v>
+        <v>983.9011279239845</v>
       </c>
       <c r="D2">
-        <v>923.1683553824688</v>
+        <v>924.2471279239845</v>
       </c>
       <c r="E2">
-        <v>-72.90000000000001</v>
+        <v>-63.054</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.846</v>
       </c>
       <c r="G2">
         <v>69.5</v>
@@ -1439,28 +1439,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4952538</v>
       </c>
       <c r="N2">
-        <v>90.90000000000001</v>
+        <v>90.40474620000001</v>
       </c>
       <c r="O2">
-        <v>11.3625</v>
+        <v>11.300593275</v>
       </c>
       <c r="P2">
-        <v>79.53750000000001</v>
+        <v>79.10415292500001</v>
       </c>
       <c r="Q2">
-        <v>80.03750000000001</v>
+        <v>79.60415292500001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09862662881175452</v>
+        <v>0.09909353083408064</v>
       </c>
       <c r="T2">
-        <v>0.890732853642657</v>
+        <v>0.8986054925006097</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>183.5422565157501</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09854272052573983</v>
+        <v>0.09845881223972514</v>
       </c>
       <c r="C3">
-        <v>983.9011279239845</v>
+        <v>975.1364246241459</v>
       </c>
       <c r="D3">
-        <v>924.2471279239845</v>
+        <v>925.3284246241459</v>
       </c>
       <c r="E3">
-        <v>-63.054</v>
+        <v>-53.20800000000001</v>
       </c>
       <c r="F3">
-        <v>9.846</v>
+        <v>19.692</v>
       </c>
       <c r="G3">
         <v>69.5</v>
@@ -1521,28 +1521,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M3">
-        <v>0.4952538</v>
+        <v>0.9905075999999999</v>
       </c>
       <c r="N3">
-        <v>90.40474620000001</v>
+        <v>89.9094924</v>
       </c>
       <c r="O3">
-        <v>11.300593275</v>
+        <v>11.23868655</v>
       </c>
       <c r="P3">
-        <v>79.10415292500001</v>
+        <v>78.67080585000001</v>
       </c>
       <c r="Q3">
-        <v>79.60415292500001</v>
+        <v>79.17080585000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09909353083408064</v>
+        <v>0.09956996146910728</v>
       </c>
       <c r="T3">
-        <v>0.8986054925006097</v>
+        <v>0.9066387974577044</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>183.5422565157501</v>
+        <v>91.77112825787506</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09845881223972514</v>
+        <v>0.09837490395371044</v>
       </c>
       <c r="C4">
-        <v>975.1364246241459</v>
+        <v>966.3742543525332</v>
       </c>
       <c r="D4">
-        <v>925.3284246241459</v>
+        <v>926.4122543525332</v>
       </c>
       <c r="E4">
-        <v>-53.20800000000001</v>
+        <v>-43.36200000000001</v>
       </c>
       <c r="F4">
-        <v>19.692</v>
+        <v>29.538</v>
       </c>
       <c r="G4">
         <v>69.5</v>
@@ -1603,28 +1603,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M4">
-        <v>0.9905075999999999</v>
+        <v>1.4857614</v>
       </c>
       <c r="N4">
-        <v>89.9094924</v>
+        <v>89.4142386</v>
       </c>
       <c r="O4">
-        <v>11.23868655</v>
+        <v>11.176779825</v>
       </c>
       <c r="P4">
-        <v>78.67080585000001</v>
+        <v>78.23745877500001</v>
       </c>
       <c r="Q4">
-        <v>79.17080585000001</v>
+        <v>78.73745877500001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09956996146910728</v>
+        <v>0.1000562154161963</v>
       </c>
       <c r="T4">
-        <v>0.9066387974577044</v>
+        <v>0.9148377375685536</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>91.77112825787506</v>
+        <v>61.18075217191671</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09837490395371044</v>
+        <v>0.09829099566769575</v>
       </c>
       <c r="C5">
-        <v>966.3742543525332</v>
+        <v>957.6146260203304</v>
       </c>
       <c r="D5">
-        <v>926.4122543525332</v>
+        <v>927.4986260203304</v>
       </c>
       <c r="E5">
-        <v>-43.36200000000001</v>
+        <v>-33.51600000000001</v>
       </c>
       <c r="F5">
-        <v>29.538</v>
+        <v>39.384</v>
       </c>
       <c r="G5">
         <v>69.5</v>
@@ -1685,28 +1685,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M5">
-        <v>1.4857614</v>
+        <v>1.9810152</v>
       </c>
       <c r="N5">
-        <v>89.4142386</v>
+        <v>88.9189848</v>
       </c>
       <c r="O5">
-        <v>11.176779825</v>
+        <v>11.1148731</v>
       </c>
       <c r="P5">
-        <v>78.23745877500001</v>
+        <v>77.80411170000001</v>
       </c>
       <c r="Q5">
-        <v>78.73745877500001</v>
+        <v>78.30411170000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1000562154161963</v>
+        <v>0.1005525996538497</v>
       </c>
       <c r="T5">
-        <v>0.9148377375685536</v>
+        <v>0.9232074889317121</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>61.18075217191671</v>
+        <v>45.88556412893753</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09829099566769575</v>
+        <v>0.09820708738168105</v>
       </c>
       <c r="C6">
-        <v>957.6146260203304</v>
+        <v>948.8575485805704</v>
       </c>
       <c r="D6">
-        <v>927.4986260203304</v>
+        <v>928.5875485805705</v>
       </c>
       <c r="E6">
-        <v>-33.51600000000001</v>
+        <v>-23.67</v>
       </c>
       <c r="F6">
-        <v>39.384</v>
+        <v>49.23</v>
       </c>
       <c r="G6">
         <v>69.5</v>
@@ -1767,28 +1767,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M6">
-        <v>1.9810152</v>
+        <v>2.476269</v>
       </c>
       <c r="N6">
-        <v>88.9189848</v>
+        <v>88.423731</v>
       </c>
       <c r="O6">
-        <v>11.1148731</v>
+        <v>11.052966375</v>
       </c>
       <c r="P6">
-        <v>77.80411170000001</v>
+        <v>77.37076462500001</v>
       </c>
       <c r="Q6">
-        <v>78.30411170000001</v>
+        <v>77.87076462500001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1005525996538497</v>
+        <v>0.1010594340859801</v>
       </c>
       <c r="T6">
-        <v>0.9232074889317121</v>
+        <v>0.9317534455867267</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.88556412893753</v>
+        <v>36.70845130315002</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09820708738168105</v>
+        <v>0.09812317909566635</v>
       </c>
       <c r="C7">
-        <v>948.8575485805704</v>
+        <v>940.1030310283802</v>
       </c>
       <c r="D7">
-        <v>928.5875485805705</v>
+        <v>929.6790310283802</v>
       </c>
       <c r="E7">
-        <v>-23.67</v>
+        <v>-13.824</v>
       </c>
       <c r="F7">
-        <v>49.23</v>
+        <v>59.07600000000001</v>
       </c>
       <c r="G7">
         <v>69.5</v>
@@ -1849,28 +1849,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M7">
-        <v>2.476269</v>
+        <v>2.9715228</v>
       </c>
       <c r="N7">
-        <v>88.423731</v>
+        <v>87.9284772</v>
       </c>
       <c r="O7">
-        <v>11.052966375</v>
+        <v>10.99105965</v>
       </c>
       <c r="P7">
-        <v>77.37076462500001</v>
+        <v>76.93741755000001</v>
       </c>
       <c r="Q7">
-        <v>77.87076462500001</v>
+        <v>77.43741755000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1010594340859801</v>
+        <v>0.1015770522294323</v>
       </c>
       <c r="T7">
-        <v>0.9317534455867267</v>
+        <v>0.9404812311067416</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.70845130315002</v>
+        <v>30.59037608595835</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09812317909566635</v>
+        <v>0.09803927080965168</v>
       </c>
       <c r="C8">
-        <v>940.1030310283802</v>
+        <v>931.3510824012287</v>
       </c>
       <c r="D8">
-        <v>929.6790310283802</v>
+        <v>930.7730824012287</v>
       </c>
       <c r="E8">
-        <v>-13.82400000000001</v>
+        <v>-3.978000000000009</v>
       </c>
       <c r="F8">
-        <v>59.076</v>
+        <v>68.922</v>
       </c>
       <c r="G8">
         <v>69.5</v>
@@ -1931,28 +1931,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M8">
-        <v>2.9715228</v>
+        <v>3.4667766</v>
       </c>
       <c r="N8">
-        <v>87.9284772</v>
+        <v>87.4332234</v>
       </c>
       <c r="O8">
-        <v>10.99105965</v>
+        <v>10.929152925</v>
       </c>
       <c r="P8">
-        <v>76.93741755000001</v>
+        <v>76.50407047500001</v>
       </c>
       <c r="Q8">
-        <v>77.43741755000001</v>
+        <v>77.00407047500001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1015770522294323</v>
+        <v>0.102105801945862</v>
       </c>
       <c r="T8">
-        <v>0.9404812311067416</v>
+        <v>0.9493967109390148</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.59037608595835</v>
+        <v>26.22032235939287</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09803927080965168</v>
+        <v>0.09795536252363699</v>
       </c>
       <c r="C9">
-        <v>931.3510824012287</v>
+        <v>922.6017117791768</v>
       </c>
       <c r="D9">
-        <v>930.7730824012287</v>
+        <v>931.8697117791768</v>
       </c>
       <c r="E9">
-        <v>-3.977999999999994</v>
+        <v>5.867999999999995</v>
       </c>
       <c r="F9">
-        <v>68.92200000000001</v>
+        <v>78.768</v>
       </c>
       <c r="G9">
         <v>69.5</v>
@@ -2013,28 +2013,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M9">
-        <v>3.4667766</v>
+        <v>3.9620304</v>
       </c>
       <c r="N9">
-        <v>87.4332234</v>
+        <v>86.9379696</v>
       </c>
       <c r="O9">
-        <v>10.929152925</v>
+        <v>10.8672462</v>
       </c>
       <c r="P9">
-        <v>76.50407047500001</v>
+        <v>76.07072340000001</v>
       </c>
       <c r="Q9">
-        <v>77.00407047500001</v>
+        <v>76.57072340000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.102105801945862</v>
+        <v>0.1026460462213445</v>
       </c>
       <c r="T9">
-        <v>0.9493967109390148</v>
+        <v>0.9585060055502506</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.22032235939287</v>
+        <v>22.94278206446877</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09795536252363699</v>
+        <v>0.09787145423762228</v>
       </c>
       <c r="C10">
-        <v>922.6017117791768</v>
+        <v>913.8549282851279</v>
       </c>
       <c r="D10">
-        <v>931.8697117791768</v>
+        <v>932.968928285128</v>
       </c>
       <c r="E10">
-        <v>5.867999999999995</v>
+        <v>15.714</v>
       </c>
       <c r="F10">
-        <v>78.768</v>
+        <v>88.614</v>
       </c>
       <c r="G10">
         <v>69.5</v>
@@ -2095,28 +2095,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M10">
-        <v>3.9620304</v>
+        <v>4.4572842</v>
       </c>
       <c r="N10">
-        <v>86.9379696</v>
+        <v>86.4427158</v>
       </c>
       <c r="O10">
-        <v>10.8672462</v>
+        <v>10.805339475</v>
       </c>
       <c r="P10">
-        <v>76.07072340000001</v>
+        <v>75.63737632500001</v>
       </c>
       <c r="Q10">
-        <v>76.57072340000001</v>
+        <v>76.13737632500001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1026460462213445</v>
+        <v>0.1031981639973871</v>
       </c>
       <c r="T10">
-        <v>0.9585060055502506</v>
+        <v>0.967815504438656</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.94278206446877</v>
+        <v>20.39358405730557</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09787145423762228</v>
+        <v>0.0977875459516076</v>
       </c>
       <c r="C11">
-        <v>913.8549282851279</v>
+        <v>905.1107410850805</v>
       </c>
       <c r="D11">
-        <v>932.968928285128</v>
+        <v>934.0707410850805</v>
       </c>
       <c r="E11">
-        <v>15.714</v>
+        <v>25.55999999999999</v>
       </c>
       <c r="F11">
-        <v>88.614</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="G11">
         <v>69.5</v>
@@ -2177,28 +2177,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M11">
-        <v>4.4572842</v>
+        <v>4.952538</v>
       </c>
       <c r="N11">
-        <v>86.4427158</v>
+        <v>85.947462</v>
       </c>
       <c r="O11">
-        <v>10.805339475</v>
+        <v>10.74343275</v>
       </c>
       <c r="P11">
-        <v>75.63737632500001</v>
+        <v>75.20402925</v>
       </c>
       <c r="Q11">
-        <v>76.13737632500001</v>
+        <v>75.70402925</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1031981639973871</v>
+        <v>0.1037625510573418</v>
       </c>
       <c r="T11">
-        <v>0.967815504438656</v>
+        <v>0.9773318810801376</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.39358405730557</v>
+        <v>18.35422565157501</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0977875459516076</v>
+        <v>0.0977036376655929</v>
       </c>
       <c r="C12">
-        <v>905.1107410850805</v>
+        <v>896.3691593883844</v>
       </c>
       <c r="D12">
-        <v>934.0707410850805</v>
+        <v>935.1751593883845</v>
       </c>
       <c r="E12">
-        <v>25.56</v>
+        <v>35.40599999999999</v>
       </c>
       <c r="F12">
-        <v>98.46000000000001</v>
+        <v>108.306</v>
       </c>
       <c r="G12">
         <v>69.5</v>
@@ -2259,28 +2259,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M12">
-        <v>4.952538000000001</v>
+        <v>5.447791799999999</v>
       </c>
       <c r="N12">
-        <v>85.947462</v>
+        <v>85.4522082</v>
       </c>
       <c r="O12">
-        <v>10.74343275</v>
+        <v>10.681526025</v>
       </c>
       <c r="P12">
-        <v>75.20402925</v>
+        <v>74.770682175</v>
       </c>
       <c r="Q12">
-        <v>75.70402925</v>
+        <v>75.270682175</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1037625510573418</v>
+        <v>0.1043396209725763</v>
       </c>
       <c r="T12">
-        <v>0.9773318810801376</v>
+        <v>0.9870621088821017</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.35422565157501</v>
+        <v>16.68565968325001</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0977036376655929</v>
+        <v>0.0976197293795782</v>
       </c>
       <c r="C13">
-        <v>896.3691593883844</v>
+        <v>887.6301924479959</v>
       </c>
       <c r="D13">
-        <v>935.1751593883845</v>
+        <v>936.282192447996</v>
       </c>
       <c r="E13">
-        <v>35.40599999999999</v>
+        <v>45.252</v>
       </c>
       <c r="F13">
-        <v>108.306</v>
+        <v>118.152</v>
       </c>
       <c r="G13">
         <v>69.5</v>
@@ -2341,28 +2341,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M13">
-        <v>5.447791799999999</v>
+        <v>5.9430456</v>
       </c>
       <c r="N13">
-        <v>85.4522082</v>
+        <v>84.9569544</v>
       </c>
       <c r="O13">
-        <v>10.681526025</v>
+        <v>10.6196193</v>
       </c>
       <c r="P13">
-        <v>74.770682175</v>
+        <v>74.3373351</v>
       </c>
       <c r="Q13">
-        <v>75.270682175</v>
+        <v>74.8373351</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1043396209725763</v>
+        <v>0.1049298061131571</v>
       </c>
       <c r="T13">
-        <v>0.9870621088821017</v>
+        <v>0.9970134782250195</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.68565968325001</v>
+        <v>15.29518804297918</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0976197293795782</v>
+        <v>0.09753582109356351</v>
       </c>
       <c r="C14">
-        <v>887.6301924479959</v>
+        <v>878.893849560737</v>
       </c>
       <c r="D14">
-        <v>936.282192447996</v>
+        <v>937.391849560737</v>
       </c>
       <c r="E14">
-        <v>45.252</v>
+        <v>55.098</v>
       </c>
       <c r="F14">
-        <v>118.152</v>
+        <v>127.998</v>
       </c>
       <c r="G14">
         <v>69.5</v>
@@ -2423,28 +2423,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M14">
-        <v>5.9430456</v>
+        <v>6.4382994</v>
       </c>
       <c r="N14">
-        <v>84.9569544</v>
+        <v>84.4617006</v>
       </c>
       <c r="O14">
-        <v>10.6196193</v>
+        <v>10.557712575</v>
       </c>
       <c r="P14">
-        <v>74.3373351</v>
+        <v>73.903988025</v>
       </c>
       <c r="Q14">
-        <v>74.8373351</v>
+        <v>74.403988025</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1049298061131571</v>
+        <v>0.1055335587282339</v>
       </c>
       <c r="T14">
-        <v>0.9970134782250195</v>
+        <v>1.007193614679269</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.29518804297918</v>
+        <v>14.11863511659616</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09753582109356351</v>
+        <v>0.09745191280754882</v>
       </c>
       <c r="C15">
-        <v>878.893849560737</v>
+        <v>870.1601400675554</v>
       </c>
       <c r="D15">
-        <v>937.391849560737</v>
+        <v>938.5041400675555</v>
       </c>
       <c r="E15">
-        <v>55.098</v>
+        <v>64.94400000000002</v>
       </c>
       <c r="F15">
-        <v>127.998</v>
+        <v>137.844</v>
       </c>
       <c r="G15">
         <v>69.5</v>
@@ -2505,28 +2505,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M15">
-        <v>6.4382994</v>
+        <v>6.9335532</v>
       </c>
       <c r="N15">
-        <v>84.4617006</v>
+        <v>83.9664468</v>
       </c>
       <c r="O15">
-        <v>10.557712575</v>
+        <v>10.49580585</v>
       </c>
       <c r="P15">
-        <v>73.903988025</v>
+        <v>73.47064095</v>
       </c>
       <c r="Q15">
-        <v>74.403988025</v>
+        <v>73.97064095</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1055335587282339</v>
+        <v>0.106151352101801</v>
       </c>
       <c r="T15">
-        <v>1.007193614679269</v>
+        <v>1.017610498492919</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.11863511659616</v>
+        <v>13.11016117969644</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09745191280754882</v>
+        <v>0.09756487952153414</v>
       </c>
       <c r="C16">
-        <v>870.1601400675554</v>
+        <v>858.8172646313517</v>
       </c>
       <c r="D16">
-        <v>938.5041400675555</v>
+        <v>937.0072646313517</v>
       </c>
       <c r="E16">
-        <v>64.94400000000002</v>
+        <v>74.79000000000002</v>
       </c>
       <c r="F16">
-        <v>137.844</v>
+        <v>147.69</v>
       </c>
       <c r="G16">
         <v>69.5</v>
@@ -2587,45 +2587,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M16">
-        <v>6.9335532</v>
+        <v>7.650342000000001</v>
       </c>
       <c r="N16">
-        <v>83.9664468</v>
+        <v>83.24965800000001</v>
       </c>
       <c r="O16">
-        <v>10.49580585</v>
+        <v>10.40620725</v>
       </c>
       <c r="P16">
-        <v>73.47064095</v>
+        <v>72.84345075000002</v>
       </c>
       <c r="Q16">
-        <v>73.97064095</v>
+        <v>73.34345075000002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.106151352101801</v>
+        <v>0.1067836817900402</v>
       </c>
       <c r="T16">
-        <v>1.017610498492919</v>
+        <v>1.028272485455126</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.11016117969644</v>
+        <v>11.881821753851</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09756487952153411</v>
+        <v>0.09749409623551944</v>
       </c>
       <c r="C17">
-        <v>858.8172646313519</v>
+        <v>849.9086256575952</v>
       </c>
       <c r="D17">
-        <v>937.007264631352</v>
+        <v>937.9446256575952</v>
       </c>
       <c r="E17">
-        <v>74.78999999999999</v>
+        <v>84.636</v>
       </c>
       <c r="F17">
-        <v>147.69</v>
+        <v>157.536</v>
       </c>
       <c r="G17">
         <v>69.5</v>
@@ -2669,28 +2669,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M17">
-        <v>7.650341999999999</v>
+        <v>8.1603648</v>
       </c>
       <c r="N17">
-        <v>83.24965800000001</v>
+        <v>82.73963520000001</v>
       </c>
       <c r="O17">
-        <v>10.40620725</v>
+        <v>10.3424544</v>
       </c>
       <c r="P17">
-        <v>72.84345075000002</v>
+        <v>72.3971808</v>
       </c>
       <c r="Q17">
-        <v>73.34345075000002</v>
+        <v>72.8971808</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1067836817900401</v>
+        <v>0.107431066947047</v>
       </c>
       <c r="T17">
-        <v>1.028272485455126</v>
+        <v>1.039188329249767</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.88182175385101</v>
+        <v>11.13920789423532</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09749409623551944</v>
+        <v>0.09742331294950474</v>
       </c>
       <c r="C18">
-        <v>849.9086256575952</v>
+        <v>841.0018639916984</v>
       </c>
       <c r="D18">
-        <v>937.9446256575952</v>
+        <v>938.8838639916985</v>
       </c>
       <c r="E18">
-        <v>84.636</v>
+        <v>94.482</v>
       </c>
       <c r="F18">
-        <v>157.536</v>
+        <v>167.382</v>
       </c>
       <c r="G18">
         <v>69.5</v>
@@ -2751,28 +2751,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M18">
-        <v>8.1603648</v>
+        <v>8.6703876</v>
       </c>
       <c r="N18">
-        <v>82.73963520000001</v>
+        <v>82.22961240000001</v>
       </c>
       <c r="O18">
-        <v>10.3424544</v>
+        <v>10.27870155</v>
       </c>
       <c r="P18">
-        <v>72.3971808</v>
+        <v>71.95091085000001</v>
       </c>
       <c r="Q18">
-        <v>72.8971808</v>
+        <v>72.45091085000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.107431066947047</v>
+        <v>0.1080940517463913</v>
       </c>
       <c r="T18">
-        <v>1.039188329249767</v>
+        <v>1.050367205425001</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.13920789423532</v>
+        <v>10.483960371045</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09742331294950474</v>
+        <v>0.09735252966349006</v>
       </c>
       <c r="C19">
-        <v>841.0018639916984</v>
+        <v>832.0969852790055</v>
       </c>
       <c r="D19">
-        <v>938.8838639916985</v>
+        <v>939.8249852790055</v>
       </c>
       <c r="E19">
-        <v>94.482</v>
+        <v>104.328</v>
       </c>
       <c r="F19">
-        <v>167.382</v>
+        <v>177.228</v>
       </c>
       <c r="G19">
         <v>69.5</v>
@@ -2833,28 +2833,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M19">
-        <v>8.6703876</v>
+        <v>9.180410400000001</v>
       </c>
       <c r="N19">
-        <v>82.22961240000001</v>
+        <v>81.71958960000001</v>
       </c>
       <c r="O19">
-        <v>10.27870155</v>
+        <v>10.2149487</v>
       </c>
       <c r="P19">
-        <v>71.95091085000001</v>
+        <v>71.5046409</v>
       </c>
       <c r="Q19">
-        <v>72.45091085000001</v>
+        <v>72.0046409</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1080940517463913</v>
+        <v>0.1087732069066952</v>
       </c>
       <c r="T19">
-        <v>1.050367205425001</v>
+        <v>1.061818737116704</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.483960371045</v>
+        <v>9.901518128209169</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09735252966349008</v>
+        <v>0.09756437137747535</v>
       </c>
       <c r="C20">
-        <v>832.0969852790054</v>
+        <v>819.4399871481919</v>
       </c>
       <c r="D20">
-        <v>939.8249852790054</v>
+        <v>937.0139871481919</v>
       </c>
       <c r="E20">
-        <v>104.328</v>
+        <v>114.174</v>
       </c>
       <c r="F20">
-        <v>177.228</v>
+        <v>187.074</v>
       </c>
       <c r="G20">
         <v>69.5</v>
@@ -2915,45 +2915,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M20">
-        <v>9.1804104</v>
+        <v>10.008459</v>
       </c>
       <c r="N20">
-        <v>81.71958960000001</v>
+        <v>80.891541</v>
       </c>
       <c r="O20">
-        <v>10.2149487</v>
+        <v>10.111442625</v>
       </c>
       <c r="P20">
-        <v>71.5046409</v>
+        <v>70.78009837500001</v>
       </c>
       <c r="Q20">
-        <v>72.0046409</v>
+        <v>71.28009837500001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1087732069066952</v>
+        <v>0.1094691313302165</v>
       </c>
       <c r="T20">
-        <v>1.061818737116704</v>
+        <v>1.073553022677338</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>9.901518128209171</v>
+        <v>9.082317267823148</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09756437137747535</v>
+        <v>0.09750846309146066</v>
       </c>
       <c r="C21">
-        <v>819.4399871481919</v>
+        <v>810.334218189766</v>
       </c>
       <c r="D21">
-        <v>937.0139871481919</v>
+        <v>937.754218189766</v>
       </c>
       <c r="E21">
-        <v>114.174</v>
+        <v>124.02</v>
       </c>
       <c r="F21">
-        <v>187.074</v>
+        <v>196.92</v>
       </c>
       <c r="G21">
         <v>69.5</v>
@@ -2997,28 +2997,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M21">
-        <v>10.008459</v>
+        <v>10.53522</v>
       </c>
       <c r="N21">
-        <v>80.891541</v>
+        <v>80.36478000000001</v>
       </c>
       <c r="O21">
-        <v>10.111442625</v>
+        <v>10.0455975</v>
       </c>
       <c r="P21">
-        <v>70.78009837500001</v>
+        <v>70.31918250000001</v>
       </c>
       <c r="Q21">
-        <v>71.28009837500001</v>
+        <v>70.81918250000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1094691313302165</v>
+        <v>0.1101824538643258</v>
       </c>
       <c r="T21">
-        <v>1.073553022677338</v>
+        <v>1.085580665376988</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.082317267823148</v>
+        <v>8.628201404431991</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09750846309146066</v>
+        <v>0.09745255480544598</v>
       </c>
       <c r="C22">
-        <v>810.334218189766</v>
+        <v>801.2296197052349</v>
       </c>
       <c r="D22">
-        <v>937.754218189766</v>
+        <v>938.4956197052348</v>
       </c>
       <c r="E22">
-        <v>124.02</v>
+        <v>133.866</v>
       </c>
       <c r="F22">
-        <v>196.92</v>
+        <v>206.766</v>
       </c>
       <c r="G22">
         <v>69.5</v>
@@ -3079,28 +3079,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M22">
-        <v>10.53522</v>
+        <v>11.061981</v>
       </c>
       <c r="N22">
-        <v>80.36478000000001</v>
+        <v>79.838019</v>
       </c>
       <c r="O22">
-        <v>10.0455975</v>
+        <v>9.979752375</v>
       </c>
       <c r="P22">
-        <v>70.31918250000001</v>
+        <v>69.858266625</v>
       </c>
       <c r="Q22">
-        <v>70.81918250000001</v>
+        <v>70.358266625</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1101824538643258</v>
+        <v>0.1109138351967671</v>
       </c>
       <c r="T22">
-        <v>1.085580665376988</v>
+        <v>1.097912805360174</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.628201404431991</v>
+        <v>8.21733467088761</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09745255480544596</v>
+        <v>0.09739664651943128</v>
       </c>
       <c r="C23">
-        <v>801.2296197052352</v>
+        <v>792.1261944729739</v>
       </c>
       <c r="D23">
-        <v>938.4956197052352</v>
+        <v>939.2381944729739</v>
       </c>
       <c r="E23">
-        <v>133.866</v>
+        <v>143.712</v>
       </c>
       <c r="F23">
-        <v>206.766</v>
+        <v>216.612</v>
       </c>
       <c r="G23">
         <v>69.5</v>
@@ -3161,28 +3161,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M23">
-        <v>11.061981</v>
+        <v>11.588742</v>
       </c>
       <c r="N23">
-        <v>79.838019</v>
+        <v>79.31125800000001</v>
       </c>
       <c r="O23">
-        <v>9.979752375</v>
+        <v>9.913907250000001</v>
       </c>
       <c r="P23">
-        <v>69.858266625</v>
+        <v>69.39735075000002</v>
       </c>
       <c r="Q23">
-        <v>70.358266625</v>
+        <v>69.89735075000002</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.110913835196767</v>
+        <v>0.1116639698967068</v>
       </c>
       <c r="T23">
-        <v>1.097912805360174</v>
+        <v>1.110561154060877</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.217334670887611</v>
+        <v>7.843819458574538</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09739664651943128</v>
+        <v>0.09750173823341658</v>
       </c>
       <c r="C24">
-        <v>792.1261944729739</v>
+        <v>780.8853347589456</v>
       </c>
       <c r="D24">
-        <v>939.2381944729739</v>
+        <v>937.8433347589457</v>
       </c>
       <c r="E24">
-        <v>143.712</v>
+        <v>153.558</v>
       </c>
       <c r="F24">
-        <v>216.612</v>
+        <v>226.458</v>
       </c>
       <c r="G24">
         <v>69.5</v>
@@ -3243,45 +3243,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M24">
-        <v>11.588742</v>
+        <v>12.2966694</v>
       </c>
       <c r="N24">
-        <v>79.31125800000001</v>
+        <v>78.60333060000001</v>
       </c>
       <c r="O24">
-        <v>9.913907250000001</v>
+        <v>9.825416325000001</v>
       </c>
       <c r="P24">
-        <v>69.39735075000002</v>
+        <v>68.777914275</v>
       </c>
       <c r="Q24">
-        <v>69.89735075000002</v>
+        <v>69.277914275</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1116639698967068</v>
+        <v>0.1124335886148267</v>
       </c>
       <c r="T24">
-        <v>1.110561154060877</v>
+        <v>1.12353803129926</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.843819458574538</v>
+        <v>7.39224557830269</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09750173823341658</v>
+        <v>0.09745282994740188</v>
       </c>
       <c r="C25">
-        <v>780.8853347589456</v>
+        <v>771.6879681687426</v>
       </c>
       <c r="D25">
-        <v>937.8433347589457</v>
+        <v>938.4919681687426</v>
       </c>
       <c r="E25">
-        <v>153.558</v>
+        <v>163.404</v>
       </c>
       <c r="F25">
-        <v>226.458</v>
+        <v>236.304</v>
       </c>
       <c r="G25">
         <v>69.5</v>
@@ -3325,28 +3325,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M25">
-        <v>12.2966694</v>
+        <v>12.8313072</v>
       </c>
       <c r="N25">
-        <v>78.60333060000001</v>
+        <v>78.06869280000001</v>
       </c>
       <c r="O25">
-        <v>9.825416325000001</v>
+        <v>9.758586600000001</v>
       </c>
       <c r="P25">
-        <v>68.777914275</v>
+        <v>68.31010620000001</v>
       </c>
       <c r="Q25">
-        <v>69.277914275</v>
+        <v>68.81010620000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1124335886148267</v>
+        <v>0.1132234604571077</v>
       </c>
       <c r="T25">
-        <v>1.12353803129926</v>
+        <v>1.136856405307075</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.39224557830269</v>
+        <v>7.084235345873412</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09745282994740188</v>
+        <v>0.09740392166138719</v>
       </c>
       <c r="C26">
-        <v>771.6879681687426</v>
+        <v>762.4914994182298</v>
       </c>
       <c r="D26">
-        <v>938.4919681687426</v>
+        <v>939.1414994182297</v>
       </c>
       <c r="E26">
-        <v>163.404</v>
+        <v>173.25</v>
       </c>
       <c r="F26">
-        <v>236.304</v>
+        <v>246.15</v>
       </c>
       <c r="G26">
         <v>69.5</v>
@@ -3407,28 +3407,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M26">
-        <v>12.8313072</v>
+        <v>13.365945</v>
       </c>
       <c r="N26">
-        <v>78.06869280000001</v>
+        <v>77.53405500000001</v>
       </c>
       <c r="O26">
-        <v>9.758586600000001</v>
+        <v>9.691756875000001</v>
       </c>
       <c r="P26">
-        <v>68.31010620000001</v>
+        <v>67.84229812500001</v>
       </c>
       <c r="Q26">
-        <v>68.81010620000001</v>
+        <v>68.34229812500001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1132234604571077</v>
+        <v>0.1140343955485162</v>
       </c>
       <c r="T26">
-        <v>1.136856405307075</v>
+        <v>1.150529935955098</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.084235345873412</v>
+        <v>6.800865932038476</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09740392166138719</v>
+        <v>0.09735501337537249</v>
       </c>
       <c r="C27">
-        <v>762.4914994182298</v>
+        <v>753.2959303728858</v>
       </c>
       <c r="D27">
-        <v>939.1414994182297</v>
+        <v>939.7919303728858</v>
       </c>
       <c r="E27">
-        <v>173.25</v>
+        <v>183.096</v>
       </c>
       <c r="F27">
-        <v>246.15</v>
+        <v>255.996</v>
       </c>
       <c r="G27">
         <v>69.5</v>
@@ -3489,28 +3489,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M27">
-        <v>13.365945</v>
+        <v>13.9005828</v>
       </c>
       <c r="N27">
-        <v>77.53405500000001</v>
+        <v>76.99941720000001</v>
       </c>
       <c r="O27">
-        <v>9.691756875000001</v>
+        <v>9.624927150000001</v>
       </c>
       <c r="P27">
-        <v>67.84229812500001</v>
+        <v>67.37449005000001</v>
       </c>
       <c r="Q27">
-        <v>68.34229812500001</v>
+        <v>67.87449005000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1140343955485162</v>
+        <v>0.1148672478045574</v>
       </c>
       <c r="T27">
-        <v>1.150529935955098</v>
+        <v>1.164573021485501</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.800865932038476</v>
+        <v>6.539294165421611</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09735501337537249</v>
+        <v>0.09730610508935782</v>
       </c>
       <c r="C28">
-        <v>753.2959303728858</v>
+        <v>744.1012629033603</v>
       </c>
       <c r="D28">
-        <v>939.7919303728858</v>
+        <v>940.4432629033604</v>
       </c>
       <c r="E28">
-        <v>183.096</v>
+        <v>192.942</v>
       </c>
       <c r="F28">
-        <v>255.996</v>
+        <v>265.842</v>
       </c>
       <c r="G28">
         <v>69.5</v>
@@ -3571,28 +3571,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M28">
-        <v>13.9005828</v>
+        <v>14.4352206</v>
       </c>
       <c r="N28">
-        <v>76.99941720000001</v>
+        <v>76.4647794</v>
       </c>
       <c r="O28">
-        <v>9.624927150000001</v>
+        <v>9.558097425</v>
       </c>
       <c r="P28">
-        <v>67.37449005000001</v>
+        <v>66.906681975</v>
       </c>
       <c r="Q28">
-        <v>67.87449005000001</v>
+        <v>67.406681975</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1148672478045574</v>
+        <v>0.1157229179306271</v>
       </c>
       <c r="T28">
-        <v>1.164573021485501</v>
+        <v>1.179000849085229</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.539294165421611</v>
+        <v>6.297098085220809</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09730610508935782</v>
+        <v>0.09750219680334311</v>
       </c>
       <c r="C29">
-        <v>744.1012629033603</v>
+        <v>731.6492573373766</v>
       </c>
       <c r="D29">
-        <v>940.4432629033604</v>
+        <v>937.8372573373767</v>
       </c>
       <c r="E29">
-        <v>192.942</v>
+        <v>202.788</v>
       </c>
       <c r="F29">
-        <v>265.842</v>
+        <v>275.688</v>
       </c>
       <c r="G29">
         <v>69.5</v>
@@ -3653,45 +3653,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M29">
-        <v>14.4352206</v>
+        <v>15.2455464</v>
       </c>
       <c r="N29">
-        <v>76.4647794</v>
+        <v>75.6544536</v>
       </c>
       <c r="O29">
-        <v>9.558097425</v>
+        <v>9.4568067</v>
       </c>
       <c r="P29">
-        <v>66.906681975</v>
+        <v>66.1976469</v>
       </c>
       <c r="Q29">
-        <v>67.406681975</v>
+        <v>66.6976469</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1157229179306271</v>
+        <v>0.1166023566713099</v>
       </c>
       <c r="T29">
-        <v>1.179000849085229</v>
+        <v>1.193829449673839</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.297098085220809</v>
+        <v>5.962396992212754</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09750219680334311</v>
+        <v>0.09746203851732843</v>
       </c>
       <c r="C30">
-        <v>731.6492573373766</v>
+        <v>722.335773354577</v>
       </c>
       <c r="D30">
-        <v>937.8372573373767</v>
+        <v>938.3697733545771</v>
       </c>
       <c r="E30">
-        <v>202.788</v>
+        <v>212.634</v>
       </c>
       <c r="F30">
-        <v>275.688</v>
+        <v>285.534</v>
       </c>
       <c r="G30">
         <v>69.5</v>
@@ -3735,28 +3735,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M30">
-        <v>15.2455464</v>
+        <v>15.7900302</v>
       </c>
       <c r="N30">
-        <v>75.6544536</v>
+        <v>75.1099698</v>
       </c>
       <c r="O30">
-        <v>9.4568067</v>
+        <v>9.388746225</v>
       </c>
       <c r="P30">
-        <v>66.1976469</v>
+        <v>65.721223575</v>
       </c>
       <c r="Q30">
-        <v>66.6976469</v>
+        <v>66.221223575</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1166023566713099</v>
+        <v>0.1175065683342654</v>
       </c>
       <c r="T30">
-        <v>1.193829449673839</v>
+        <v>1.209075757321283</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.962396992212754</v>
+        <v>5.756797095929556</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0974620385173284</v>
+        <v>0.09742188023131372</v>
       </c>
       <c r="C31">
-        <v>722.3357733545776</v>
+        <v>713.0228944541936</v>
       </c>
       <c r="D31">
-        <v>938.3697733545775</v>
+        <v>938.9028944541936</v>
       </c>
       <c r="E31">
-        <v>212.634</v>
+        <v>222.48</v>
       </c>
       <c r="F31">
-        <v>285.534</v>
+        <v>295.38</v>
       </c>
       <c r="G31">
         <v>69.5</v>
@@ -3817,28 +3817,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M31">
-        <v>15.7900302</v>
+        <v>16.334514</v>
       </c>
       <c r="N31">
-        <v>75.1099698</v>
+        <v>74.56548600000001</v>
       </c>
       <c r="O31">
-        <v>9.388746225</v>
+        <v>9.320685750000001</v>
       </c>
       <c r="P31">
-        <v>65.721223575</v>
+        <v>65.24480025000001</v>
       </c>
       <c r="Q31">
-        <v>66.221223575</v>
+        <v>65.74480025000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1175065683342654</v>
+        <v>0.1184366146161625</v>
       </c>
       <c r="T31">
-        <v>1.209075757321282</v>
+        <v>1.224757673758653</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.756797095929556</v>
+        <v>5.564903859398572</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09742188023131372</v>
+        <v>0.09738172194529902</v>
       </c>
       <c r="C32">
-        <v>713.0228944541936</v>
+        <v>703.7106216681181</v>
       </c>
       <c r="D32">
-        <v>938.9028944541936</v>
+        <v>939.4366216681181</v>
       </c>
       <c r="E32">
-        <v>222.48</v>
+        <v>232.326</v>
       </c>
       <c r="F32">
-        <v>295.38</v>
+        <v>305.226</v>
       </c>
       <c r="G32">
         <v>69.5</v>
@@ -3899,28 +3899,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M32">
-        <v>16.334514</v>
+        <v>16.8789978</v>
       </c>
       <c r="N32">
-        <v>74.56548600000001</v>
+        <v>74.0210022</v>
       </c>
       <c r="O32">
-        <v>9.320685750000001</v>
+        <v>9.252625275</v>
       </c>
       <c r="P32">
-        <v>65.24480025000001</v>
+        <v>64.768376925</v>
       </c>
       <c r="Q32">
-        <v>65.74480025000001</v>
+        <v>65.268376925</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1184366146161625</v>
+        <v>0.1193936187613029</v>
       </c>
       <c r="T32">
-        <v>1.224757673758653</v>
+        <v>1.240894138498557</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.564903859398572</v>
+        <v>5.385390831676037</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09738172194529902</v>
+        <v>0.09734156365928434</v>
       </c>
       <c r="C33">
-        <v>703.7106216681181</v>
+        <v>694.398956030591</v>
       </c>
       <c r="D33">
-        <v>939.4366216681181</v>
+        <v>939.970956030591</v>
       </c>
       <c r="E33">
-        <v>232.326</v>
+        <v>242.172</v>
       </c>
       <c r="F33">
-        <v>305.226</v>
+        <v>315.072</v>
       </c>
       <c r="G33">
         <v>69.5</v>
@@ -3981,28 +3981,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M33">
-        <v>16.8789978</v>
+        <v>17.4234816</v>
       </c>
       <c r="N33">
-        <v>74.0210022</v>
+        <v>73.4765184</v>
       </c>
       <c r="O33">
-        <v>9.252625275</v>
+        <v>9.1845648</v>
       </c>
       <c r="P33">
-        <v>64.768376925</v>
+        <v>64.2919536</v>
       </c>
       <c r="Q33">
-        <v>65.268376925</v>
+        <v>64.7919536</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1193936187613029</v>
+        <v>0.1203787700871829</v>
       </c>
       <c r="T33">
-        <v>1.240894138498557</v>
+        <v>1.257505205142575</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.385390831676037</v>
+        <v>5.217097368186161</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09734156365928434</v>
+        <v>0.09730140537326964</v>
       </c>
       <c r="C34">
-        <v>694.398956030591</v>
+        <v>685.0878985782067</v>
       </c>
       <c r="D34">
-        <v>939.970956030591</v>
+        <v>940.5058985782067</v>
       </c>
       <c r="E34">
-        <v>242.172</v>
+        <v>252.018</v>
       </c>
       <c r="F34">
-        <v>315.072</v>
+        <v>324.918</v>
       </c>
       <c r="G34">
         <v>69.5</v>
@@ -4063,28 +4063,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M34">
-        <v>17.4234816</v>
+        <v>17.9679654</v>
       </c>
       <c r="N34">
-        <v>73.4765184</v>
+        <v>72.93203460000001</v>
       </c>
       <c r="O34">
-        <v>9.1845648</v>
+        <v>9.116504325000001</v>
       </c>
       <c r="P34">
-        <v>64.2919536</v>
+        <v>63.81553027500001</v>
       </c>
       <c r="Q34">
-        <v>64.7919536</v>
+        <v>64.31553027500001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1203787700871829</v>
+        <v>0.1213933289153278</v>
       </c>
       <c r="T34">
-        <v>1.257505205142575</v>
+        <v>1.274612124522235</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.217097368186161</v>
+        <v>5.059003508544157</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09730140537326964</v>
+        <v>0.09726124708725496</v>
       </c>
       <c r="C35">
-        <v>685.0878985782067</v>
+        <v>675.7774503499212</v>
       </c>
       <c r="D35">
-        <v>940.5058985782067</v>
+        <v>941.0414503499212</v>
       </c>
       <c r="E35">
-        <v>252.018</v>
+        <v>261.864</v>
       </c>
       <c r="F35">
-        <v>324.918</v>
+        <v>334.764</v>
       </c>
       <c r="G35">
         <v>69.5</v>
@@ -4145,28 +4145,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M35">
-        <v>17.9679654</v>
+        <v>18.5124492</v>
       </c>
       <c r="N35">
-        <v>72.93203460000001</v>
+        <v>72.3875508</v>
       </c>
       <c r="O35">
-        <v>9.116504325000001</v>
+        <v>9.04844385</v>
       </c>
       <c r="P35">
-        <v>63.81553027500001</v>
+        <v>63.33910695</v>
       </c>
       <c r="Q35">
-        <v>64.31553027500001</v>
+        <v>63.83910695</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1213933289153278</v>
+        <v>0.1224386319503863</v>
       </c>
       <c r="T35">
-        <v>1.274612124522235</v>
+        <v>1.292237435398249</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.059003508544157</v>
+        <v>4.910209287704621</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09726124708725496</v>
+        <v>0.09722108880124025</v>
       </c>
       <c r="C36">
-        <v>675.7774503499212</v>
+        <v>666.4676123870579</v>
       </c>
       <c r="D36">
-        <v>941.0414503499212</v>
+        <v>941.5776123870579</v>
       </c>
       <c r="E36">
-        <v>261.864</v>
+        <v>271.71</v>
       </c>
       <c r="F36">
-        <v>334.764</v>
+        <v>344.61</v>
       </c>
       <c r="G36">
         <v>69.5</v>
@@ -4227,28 +4227,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M36">
-        <v>18.5124492</v>
+        <v>19.056933</v>
       </c>
       <c r="N36">
-        <v>72.3875508</v>
+        <v>71.843067</v>
       </c>
       <c r="O36">
-        <v>9.04844385</v>
+        <v>8.980383375000001</v>
       </c>
       <c r="P36">
-        <v>63.33910695</v>
+        <v>62.862683625</v>
       </c>
       <c r="Q36">
-        <v>63.83910695</v>
+        <v>63.362683625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1224386319503863</v>
+        <v>0.1235160981557543</v>
       </c>
       <c r="T36">
-        <v>1.292237435398249</v>
+        <v>1.310405063531986</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.910209287704621</v>
+        <v>4.769917593770204</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09722108880124025</v>
+        <v>0.09718093051522557</v>
       </c>
       <c r="C37">
-        <v>666.4676123870579</v>
+        <v>657.1583857333142</v>
       </c>
       <c r="D37">
-        <v>941.5776123870579</v>
+        <v>942.1143857333143</v>
       </c>
       <c r="E37">
-        <v>271.71</v>
+        <v>281.556</v>
       </c>
       <c r="F37">
-        <v>344.61</v>
+        <v>354.4560000000001</v>
       </c>
       <c r="G37">
         <v>69.5</v>
@@ -4309,28 +4309,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M37">
-        <v>19.056933</v>
+        <v>19.60141680000001</v>
       </c>
       <c r="N37">
-        <v>71.843067</v>
+        <v>71.2985832</v>
       </c>
       <c r="O37">
-        <v>8.980383375000001</v>
+        <v>8.912322899999999</v>
       </c>
       <c r="P37">
-        <v>62.862683625</v>
+        <v>62.3862603</v>
       </c>
       <c r="Q37">
-        <v>63.362683625</v>
+        <v>62.8862603</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1235160981557543</v>
+        <v>0.12462723518004</v>
       </c>
       <c r="T37">
-        <v>1.310405063531986</v>
+        <v>1.329140430044902</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.769917593770204</v>
+        <v>4.637419882832141</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09718093051522558</v>
+        <v>0.09714077222921087</v>
       </c>
       <c r="C38">
-        <v>657.158385733314</v>
+        <v>647.8497714347699</v>
       </c>
       <c r="D38">
-        <v>942.1143857333141</v>
+        <v>942.6517714347699</v>
       </c>
       <c r="E38">
-        <v>281.556</v>
+        <v>291.402</v>
       </c>
       <c r="F38">
-        <v>354.456</v>
+        <v>364.302</v>
       </c>
       <c r="G38">
         <v>69.5</v>
@@ -4391,28 +4391,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M38">
-        <v>19.6014168</v>
+        <v>20.1459006</v>
       </c>
       <c r="N38">
-        <v>71.2985832</v>
+        <v>70.7540994</v>
       </c>
       <c r="O38">
-        <v>8.912322899999999</v>
+        <v>8.844262425</v>
       </c>
       <c r="P38">
-        <v>62.3862603</v>
+        <v>61.909836975</v>
       </c>
       <c r="Q38">
-        <v>62.8862603</v>
+        <v>62.409836975</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.12462723518004</v>
+        <v>0.1257736463955728</v>
       </c>
       <c r="T38">
-        <v>1.329140430044902</v>
+        <v>1.348470570097911</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.637419882832143</v>
+        <v>4.512084210323167</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09714077222921087</v>
+        <v>0.09793186394319618</v>
       </c>
       <c r="C39">
-        <v>647.8497714347699</v>
+        <v>627.5292870075579</v>
       </c>
       <c r="D39">
-        <v>942.6517714347699</v>
+        <v>932.1772870075579</v>
       </c>
       <c r="E39">
-        <v>291.402</v>
+        <v>301.248</v>
       </c>
       <c r="F39">
-        <v>364.302</v>
+        <v>374.148</v>
       </c>
       <c r="G39">
         <v>69.5</v>
@@ -4473,45 +4473,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M39">
-        <v>20.1459006</v>
+        <v>21.6257544</v>
       </c>
       <c r="N39">
-        <v>70.7540994</v>
+        <v>69.2742456</v>
       </c>
       <c r="O39">
-        <v>8.844262425</v>
+        <v>8.6592807</v>
       </c>
       <c r="P39">
-        <v>61.909836975</v>
+        <v>60.6149649</v>
       </c>
       <c r="Q39">
-        <v>62.409836975</v>
+        <v>61.1149649</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1257736463955728</v>
+        <v>0.1269570386180583</v>
       </c>
       <c r="T39">
-        <v>1.348470570097911</v>
+        <v>1.368424263055856</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.512084210323167</v>
+        <v>4.203321572911232</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09793186394319618</v>
+        <v>0.09791358065718149</v>
       </c>
       <c r="C40">
-        <v>627.5292870075579</v>
+        <v>617.9227392158346</v>
       </c>
       <c r="D40">
-        <v>932.1772870075579</v>
+        <v>932.4167392158346</v>
       </c>
       <c r="E40">
-        <v>301.248</v>
+        <v>311.0940000000001</v>
       </c>
       <c r="F40">
-        <v>374.148</v>
+        <v>383.994</v>
       </c>
       <c r="G40">
         <v>69.5</v>
@@ -4555,28 +4555,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M40">
-        <v>21.6257544</v>
+        <v>22.1948532</v>
       </c>
       <c r="N40">
-        <v>69.2742456</v>
+        <v>68.70514679999999</v>
       </c>
       <c r="O40">
-        <v>8.6592807</v>
+        <v>8.588143349999999</v>
       </c>
       <c r="P40">
-        <v>60.6149649</v>
+        <v>60.11700345</v>
       </c>
       <c r="Q40">
-        <v>61.1149649</v>
+        <v>60.61700345</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1269570386180583</v>
+        <v>0.1281792305855434</v>
       </c>
       <c r="T40">
-        <v>1.368424263055856</v>
+        <v>1.389032175455045</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.203321572911232</v>
+        <v>4.095544096682739</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09791358065718149</v>
+        <v>0.0991202973711668</v>
       </c>
       <c r="C41">
-        <v>617.9227392158346</v>
+        <v>592.532117057223</v>
       </c>
       <c r="D41">
-        <v>932.4167392158346</v>
+        <v>916.872117057223</v>
       </c>
       <c r="E41">
-        <v>311.0940000000001</v>
+        <v>320.9400000000001</v>
       </c>
       <c r="F41">
-        <v>383.994</v>
+        <v>393.84</v>
       </c>
       <c r="G41">
         <v>69.5</v>
@@ -4637,45 +4637,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M41">
-        <v>22.1948532</v>
+        <v>24.142392</v>
       </c>
       <c r="N41">
-        <v>68.70514679999999</v>
+        <v>66.757608</v>
       </c>
       <c r="O41">
-        <v>8.588143349999999</v>
+        <v>8.344701000000001</v>
       </c>
       <c r="P41">
-        <v>60.11700345</v>
+        <v>58.412907</v>
       </c>
       <c r="Q41">
-        <v>60.61700345</v>
+        <v>58.912907</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1281792305855434</v>
+        <v>0.129442162285278</v>
       </c>
       <c r="T41">
-        <v>1.389032175455045</v>
+        <v>1.41032701826754</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.095544096682739</v>
+        <v>3.765161298018854</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0991202973711668</v>
+        <v>0.0991326390851521</v>
       </c>
       <c r="C42">
-        <v>592.532117057223</v>
+        <v>582.5298112980731</v>
       </c>
       <c r="D42">
-        <v>916.872117057223</v>
+        <v>916.7158112980732</v>
       </c>
       <c r="E42">
-        <v>320.9400000000001</v>
+        <v>330.7860000000001</v>
       </c>
       <c r="F42">
-        <v>393.84</v>
+        <v>403.686</v>
       </c>
       <c r="G42">
         <v>69.5</v>
@@ -4719,28 +4719,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M42">
-        <v>24.142392</v>
+        <v>24.7459518</v>
       </c>
       <c r="N42">
-        <v>66.757608</v>
+        <v>66.15404820000001</v>
       </c>
       <c r="O42">
-        <v>8.344701000000001</v>
+        <v>8.269256025000001</v>
       </c>
       <c r="P42">
-        <v>58.412907</v>
+        <v>57.884792175</v>
       </c>
       <c r="Q42">
-        <v>58.912907</v>
+        <v>58.384792175</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.129442162285278</v>
+        <v>0.1307479052290714</v>
       </c>
       <c r="T42">
-        <v>1.41032701826754</v>
+        <v>1.432343720158425</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.765161298018854</v>
+        <v>3.67332809562815</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0991326390851521</v>
+        <v>0.09914498079913742</v>
       </c>
       <c r="C43">
-        <v>582.5298112980731</v>
+        <v>572.5275588229647</v>
       </c>
       <c r="D43">
-        <v>916.7158112980732</v>
+        <v>916.5595588229647</v>
       </c>
       <c r="E43">
-        <v>330.7860000000001</v>
+        <v>340.6320000000001</v>
       </c>
       <c r="F43">
-        <v>403.686</v>
+        <v>413.532</v>
       </c>
       <c r="G43">
         <v>69.5</v>
@@ -4801,28 +4801,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M43">
-        <v>24.7459518</v>
+        <v>25.3495116</v>
       </c>
       <c r="N43">
-        <v>66.15404820000001</v>
+        <v>65.55048840000001</v>
       </c>
       <c r="O43">
-        <v>8.269256025000001</v>
+        <v>8.193811050000001</v>
       </c>
       <c r="P43">
-        <v>57.884792175</v>
+        <v>57.35667735000001</v>
       </c>
       <c r="Q43">
-        <v>58.384792175</v>
+        <v>57.85667735000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1307479052290714</v>
+        <v>0.1320986737916162</v>
       </c>
       <c r="T43">
-        <v>1.432343720158425</v>
+        <v>1.455119618666237</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.67332809562815</v>
+        <v>3.585867902875099</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09914498079913742</v>
+        <v>0.0991573225131227</v>
       </c>
       <c r="C44">
-        <v>572.5275588229647</v>
+        <v>562.5253596046564</v>
       </c>
       <c r="D44">
-        <v>916.5595588229647</v>
+        <v>916.4033596046563</v>
       </c>
       <c r="E44">
-        <v>340.6319999999999</v>
+        <v>350.478</v>
       </c>
       <c r="F44">
-        <v>413.532</v>
+        <v>423.378</v>
       </c>
       <c r="G44">
         <v>69.5</v>
@@ -4883,28 +4883,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M44">
-        <v>25.3495116</v>
+        <v>25.9530714</v>
       </c>
       <c r="N44">
-        <v>65.55048840000001</v>
+        <v>64.94692860000001</v>
       </c>
       <c r="O44">
-        <v>8.193811050000001</v>
+        <v>8.118366075000001</v>
       </c>
       <c r="P44">
-        <v>57.35667735000001</v>
+        <v>56.82856252500001</v>
       </c>
       <c r="Q44">
-        <v>57.85667735000001</v>
+        <v>57.32856252500001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1320986737916162</v>
+        <v>0.1334968377423205</v>
       </c>
       <c r="T44">
-        <v>1.455119618666237</v>
+        <v>1.478694671507656</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.585867902875099</v>
+        <v>3.502475626064051</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0991573225131227</v>
+        <v>0.100247664227108</v>
       </c>
       <c r="C45">
-        <v>562.5253596046564</v>
+        <v>539.0867748801816</v>
       </c>
       <c r="D45">
-        <v>916.4033596046563</v>
+        <v>902.8107748801815</v>
       </c>
       <c r="E45">
-        <v>350.478</v>
+        <v>360.324</v>
       </c>
       <c r="F45">
-        <v>423.378</v>
+        <v>433.224</v>
       </c>
       <c r="G45">
         <v>69.5</v>
@@ -4965,45 +4965,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M45">
-        <v>25.9530714</v>
+        <v>27.7696584</v>
       </c>
       <c r="N45">
-        <v>64.94692860000001</v>
+        <v>63.13034160000001</v>
       </c>
       <c r="O45">
-        <v>8.118366075000001</v>
+        <v>7.891292700000001</v>
       </c>
       <c r="P45">
-        <v>56.82856252500001</v>
+        <v>55.23904890000001</v>
       </c>
       <c r="Q45">
-        <v>57.32856252500001</v>
+        <v>55.73904890000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1334968377423205</v>
+        <v>0.1349449361198358</v>
       </c>
       <c r="T45">
-        <v>1.478694671507656</v>
+        <v>1.503111690521984</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.502475626064051</v>
+        <v>3.273356794334928</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.100247664227108</v>
+        <v>0.1002845059410933</v>
       </c>
       <c r="C46">
-        <v>539.0867748801816</v>
+        <v>528.7885320355276</v>
       </c>
       <c r="D46">
-        <v>902.8107748801815</v>
+        <v>902.3585320355276</v>
       </c>
       <c r="E46">
-        <v>360.324</v>
+        <v>370.17</v>
       </c>
       <c r="F46">
-        <v>433.224</v>
+        <v>443.07</v>
       </c>
       <c r="G46">
         <v>69.5</v>
@@ -5047,28 +5047,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M46">
-        <v>27.7696584</v>
+        <v>28.400787</v>
       </c>
       <c r="N46">
-        <v>63.13034160000001</v>
+        <v>62.499213</v>
       </c>
       <c r="O46">
-        <v>7.891292700000001</v>
+        <v>7.812401625000001</v>
       </c>
       <c r="P46">
-        <v>55.23904890000001</v>
+        <v>54.686811375</v>
       </c>
       <c r="Q46">
-        <v>55.73904890000001</v>
+        <v>55.186811375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1349449361198358</v>
+        <v>0.1364456926201697</v>
       </c>
       <c r="T46">
-        <v>1.503111690521984</v>
+        <v>1.528416601136832</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.273356794334928</v>
+        <v>3.200615532238596</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1002845059410933</v>
+        <v>0.1003213476550787</v>
       </c>
       <c r="C47">
-        <v>528.7885320355276</v>
+        <v>518.4907420458813</v>
       </c>
       <c r="D47">
-        <v>902.3585320355276</v>
+        <v>901.9067420458814</v>
       </c>
       <c r="E47">
-        <v>370.17</v>
+        <v>380.0160000000001</v>
       </c>
       <c r="F47">
-        <v>443.07</v>
+        <v>452.9160000000001</v>
       </c>
       <c r="G47">
         <v>69.5</v>
@@ -5129,28 +5129,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M47">
-        <v>28.400787</v>
+        <v>29.0319156</v>
       </c>
       <c r="N47">
-        <v>62.499213</v>
+        <v>61.8680844</v>
       </c>
       <c r="O47">
-        <v>7.812401625000001</v>
+        <v>7.73351055</v>
       </c>
       <c r="P47">
-        <v>54.686811375</v>
+        <v>54.13457385</v>
       </c>
       <c r="Q47">
-        <v>55.186811375</v>
+        <v>54.63457385</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1364456926201697</v>
+        <v>0.1380020326945901</v>
       </c>
       <c r="T47">
-        <v>1.528416601136832</v>
+        <v>1.554658730663341</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.200615532238596</v>
+        <v>3.13103693371167</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1003213476550787</v>
+        <v>0.1003581893690639</v>
       </c>
       <c r="C48">
-        <v>518.4907420458813</v>
+        <v>508.1934042313821</v>
       </c>
       <c r="D48">
-        <v>901.9067420458814</v>
+        <v>901.4554042313822</v>
       </c>
       <c r="E48">
-        <v>380.0160000000001</v>
+        <v>389.8620000000001</v>
       </c>
       <c r="F48">
-        <v>452.9160000000001</v>
+        <v>462.7620000000001</v>
       </c>
       <c r="G48">
         <v>69.5</v>
@@ -5211,28 +5211,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M48">
-        <v>29.0319156</v>
+        <v>29.66304420000001</v>
       </c>
       <c r="N48">
-        <v>61.8680844</v>
+        <v>61.2369558</v>
       </c>
       <c r="O48">
-        <v>7.73351055</v>
+        <v>7.654619475000001</v>
       </c>
       <c r="P48">
-        <v>54.13457385</v>
+        <v>53.582336325</v>
       </c>
       <c r="Q48">
-        <v>54.63457385</v>
+        <v>54.082336325</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1380020326945901</v>
+        <v>0.1396171025831395</v>
       </c>
       <c r="T48">
-        <v>1.554658730663341</v>
+        <v>1.581891129228586</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.13103693371167</v>
+        <v>3.064419126611421</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1003581893690639</v>
+        <v>0.1003950310830493</v>
       </c>
       <c r="C49">
-        <v>508.1934042313821</v>
+        <v>497.8965179135272</v>
       </c>
       <c r="D49">
-        <v>901.4554042313822</v>
+        <v>901.0045179135273</v>
       </c>
       <c r="E49">
-        <v>389.8620000000001</v>
+        <v>399.7080000000001</v>
       </c>
       <c r="F49">
-        <v>462.7620000000001</v>
+        <v>472.6080000000001</v>
       </c>
       <c r="G49">
         <v>69.5</v>
@@ -5293,28 +5293,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M49">
-        <v>29.66304420000001</v>
+        <v>30.29417280000001</v>
       </c>
       <c r="N49">
-        <v>61.2369558</v>
+        <v>60.6058272</v>
       </c>
       <c r="O49">
-        <v>7.654619475000001</v>
+        <v>7.5757284</v>
       </c>
       <c r="P49">
-        <v>53.582336325</v>
+        <v>53.0300988</v>
       </c>
       <c r="Q49">
-        <v>54.082336325</v>
+        <v>53.5300988</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1396171025831395</v>
+        <v>0.1412942905443255</v>
       </c>
       <c r="T49">
-        <v>1.581891129228586</v>
+        <v>1.610170927738649</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.064419126611421</v>
+        <v>3.000577061473683</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1003950310830492</v>
+        <v>0.1037761227970346</v>
       </c>
       <c r="C50">
-        <v>497.8965179135274</v>
+        <v>448.5069779815172</v>
       </c>
       <c r="D50">
-        <v>901.0045179135274</v>
+        <v>861.4609779815172</v>
       </c>
       <c r="E50">
-        <v>399.708</v>
+        <v>409.554</v>
       </c>
       <c r="F50">
-        <v>472.608</v>
+        <v>482.454</v>
       </c>
       <c r="G50">
         <v>69.5</v>
@@ -5375,45 +5375,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M50">
-        <v>30.2941728</v>
+        <v>34.6884426</v>
       </c>
       <c r="N50">
-        <v>60.60582720000001</v>
+        <v>56.2115574</v>
       </c>
       <c r="O50">
-        <v>7.575728400000001</v>
+        <v>7.026444675</v>
       </c>
       <c r="P50">
-        <v>53.0300988</v>
+        <v>49.185112725</v>
       </c>
       <c r="Q50">
-        <v>53.5300988</v>
+        <v>49.685112725</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1412942905443255</v>
+        <v>0.1430372505824207</v>
       </c>
       <c r="T50">
-        <v>1.610170927738649</v>
+        <v>1.639559737954989</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.000577061473684</v>
+        <v>2.620469331765272</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1037761227970346</v>
+        <v>0.1038812145110199</v>
       </c>
       <c r="C51">
-        <v>448.5069779815172</v>
+        <v>437.4874223731437</v>
       </c>
       <c r="D51">
-        <v>861.4609779815172</v>
+        <v>860.2874223731437</v>
       </c>
       <c r="E51">
-        <v>409.554</v>
+        <v>419.4</v>
       </c>
       <c r="F51">
-        <v>482.454</v>
+        <v>492.3</v>
       </c>
       <c r="G51">
         <v>69.5</v>
@@ -5457,28 +5457,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M51">
-        <v>34.6884426</v>
+        <v>35.39637</v>
       </c>
       <c r="N51">
-        <v>56.2115574</v>
+        <v>55.50363</v>
       </c>
       <c r="O51">
-        <v>7.026444675</v>
+        <v>6.93795375</v>
       </c>
       <c r="P51">
-        <v>49.185112725</v>
+        <v>48.56567625</v>
       </c>
       <c r="Q51">
-        <v>49.685112725</v>
+        <v>49.06567625</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1430372505824207</v>
+        <v>0.1448499290220397</v>
       </c>
       <c r="T51">
-        <v>1.639559737954989</v>
+        <v>1.670124100579982</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.620469331765272</v>
+        <v>2.568059945129967</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1038812145110199</v>
+        <v>0.1039863062250052</v>
       </c>
       <c r="C52">
-        <v>437.4874223731437</v>
+        <v>426.471059849935</v>
       </c>
       <c r="D52">
-        <v>860.2874223731437</v>
+        <v>859.117059849935</v>
       </c>
       <c r="E52">
-        <v>419.4</v>
+        <v>429.246</v>
       </c>
       <c r="F52">
-        <v>492.3</v>
+        <v>502.146</v>
       </c>
       <c r="G52">
         <v>69.5</v>
@@ -5539,28 +5539,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M52">
-        <v>35.39637</v>
+        <v>36.10429740000001</v>
       </c>
       <c r="N52">
-        <v>55.50363</v>
+        <v>54.7957026</v>
       </c>
       <c r="O52">
-        <v>6.93795375</v>
+        <v>6.849462825</v>
       </c>
       <c r="P52">
-        <v>48.56567625</v>
+        <v>47.946239775</v>
       </c>
       <c r="Q52">
-        <v>49.06567625</v>
+        <v>48.446239775</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1448499290220397</v>
+        <v>0.1467365943367453</v>
       </c>
       <c r="T52">
-        <v>1.670124100579982</v>
+        <v>1.701935988210077</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.568059945129967</v>
+        <v>2.517705828558791</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1039863062250052</v>
+        <v>0.1058658979389905</v>
       </c>
       <c r="C53">
-        <v>426.471059849935</v>
+        <v>396.2178503288714</v>
       </c>
       <c r="D53">
-        <v>859.117059849935</v>
+        <v>838.7098503288714</v>
       </c>
       <c r="E53">
-        <v>429.246</v>
+        <v>439.092</v>
       </c>
       <c r="F53">
-        <v>502.146</v>
+        <v>511.992</v>
       </c>
       <c r="G53">
         <v>69.5</v>
@@ -5621,45 +5621,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M53">
-        <v>36.10429740000001</v>
+        <v>38.80899360000001</v>
       </c>
       <c r="N53">
-        <v>54.7957026</v>
+        <v>52.0910064</v>
       </c>
       <c r="O53">
-        <v>6.849462825</v>
+        <v>6.5113758</v>
       </c>
       <c r="P53">
-        <v>47.946239775</v>
+        <v>45.5796306</v>
       </c>
       <c r="Q53">
-        <v>48.446239775</v>
+        <v>46.0796306</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1467365943367453</v>
+        <v>0.1487018707062302</v>
       </c>
       <c r="T53">
-        <v>1.701935988210077</v>
+        <v>1.735073371158092</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.125</v>
       </c>
       <c r="W53">
-        <v>0.06291250000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.517705828558791</v>
+        <v>2.342240588274363</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1058658979389905</v>
+        <v>0.1060051146529758</v>
       </c>
       <c r="C54">
-        <v>396.2178503288714</v>
+        <v>384.898834329323</v>
       </c>
       <c r="D54">
-        <v>838.7098503288714</v>
+        <v>837.2368343293231</v>
       </c>
       <c r="E54">
-        <v>439.092</v>
+        <v>448.9380000000001</v>
       </c>
       <c r="F54">
-        <v>511.992</v>
+        <v>521.8380000000001</v>
       </c>
       <c r="G54">
         <v>69.5</v>
@@ -5703,28 +5703,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M54">
-        <v>38.80899360000001</v>
+        <v>39.55532040000001</v>
       </c>
       <c r="N54">
-        <v>52.0910064</v>
+        <v>51.3446796</v>
       </c>
       <c r="O54">
-        <v>6.5113758</v>
+        <v>6.41808495</v>
       </c>
       <c r="P54">
-        <v>45.5796306</v>
+        <v>44.92659465</v>
       </c>
       <c r="Q54">
-        <v>46.0796306</v>
+        <v>45.42659465</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1487018707062302</v>
+        <v>0.1507507758573953</v>
       </c>
       <c r="T54">
-        <v>1.735073371158092</v>
+        <v>1.769620855508151</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.342240588274363</v>
+        <v>2.298047369627677</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1060051146529758</v>
+        <v>0.1061443313669611</v>
       </c>
       <c r="C55">
-        <v>384.898834329323</v>
+        <v>373.5849833390171</v>
       </c>
       <c r="D55">
-        <v>837.2368343293231</v>
+        <v>835.7689833390172</v>
       </c>
       <c r="E55">
-        <v>448.9380000000001</v>
+        <v>458.7840000000001</v>
       </c>
       <c r="F55">
-        <v>521.8380000000001</v>
+        <v>531.6840000000001</v>
       </c>
       <c r="G55">
         <v>69.5</v>
@@ -5785,28 +5785,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M55">
-        <v>39.55532040000001</v>
+        <v>40.30164720000001</v>
       </c>
       <c r="N55">
-        <v>51.3446796</v>
+        <v>50.59835279999999</v>
       </c>
       <c r="O55">
-        <v>6.41808495</v>
+        <v>6.324794099999999</v>
       </c>
       <c r="P55">
-        <v>44.92659465</v>
+        <v>44.2735587</v>
       </c>
       <c r="Q55">
-        <v>45.42659465</v>
+        <v>44.7735587</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1507507758573953</v>
+        <v>0.1528887638412198</v>
       </c>
       <c r="T55">
-        <v>1.769620855508151</v>
+        <v>1.805670404395169</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.298047369627677</v>
+        <v>2.255490936856794</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1061443313669611</v>
+        <v>0.1062835480809464</v>
       </c>
       <c r="C56">
-        <v>373.5849833390171</v>
+        <v>362.2762702394788</v>
       </c>
       <c r="D56">
-        <v>835.7689833390172</v>
+        <v>834.3062702394789</v>
       </c>
       <c r="E56">
-        <v>458.7840000000001</v>
+        <v>468.6300000000001</v>
       </c>
       <c r="F56">
-        <v>531.6840000000001</v>
+        <v>541.5300000000001</v>
       </c>
       <c r="G56">
         <v>69.5</v>
@@ -5867,28 +5867,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M56">
-        <v>40.30164720000001</v>
+        <v>41.04797400000001</v>
       </c>
       <c r="N56">
-        <v>50.59835279999999</v>
+        <v>49.852026</v>
       </c>
       <c r="O56">
-        <v>6.324794099999999</v>
+        <v>6.231503249999999</v>
       </c>
       <c r="P56">
-        <v>44.2735587</v>
+        <v>43.62052274999999</v>
       </c>
       <c r="Q56">
-        <v>44.7735587</v>
+        <v>44.12052274999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1528887638412198</v>
+        <v>0.1551217735132142</v>
       </c>
       <c r="T56">
-        <v>1.805670404395169</v>
+        <v>1.843322155454943</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.255490936856794</v>
+        <v>2.214482010732125</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1062835480809464</v>
+        <v>0.1064227647949317</v>
       </c>
       <c r="C57">
-        <v>362.2762702394788</v>
+        <v>350.9726681017465</v>
       </c>
       <c r="D57">
-        <v>834.3062702394789</v>
+        <v>832.8486681017466</v>
       </c>
       <c r="E57">
-        <v>468.6300000000001</v>
+        <v>478.4760000000001</v>
       </c>
       <c r="F57">
-        <v>541.5300000000001</v>
+        <v>551.3760000000001</v>
       </c>
       <c r="G57">
         <v>69.5</v>
@@ -5949,28 +5949,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M57">
-        <v>41.04797400000001</v>
+        <v>41.79430080000001</v>
       </c>
       <c r="N57">
-        <v>49.852026</v>
+        <v>49.1056992</v>
       </c>
       <c r="O57">
-        <v>6.231503249999999</v>
+        <v>6.1382124</v>
       </c>
       <c r="P57">
-        <v>43.62052274999999</v>
+        <v>42.9674868</v>
       </c>
       <c r="Q57">
-        <v>44.12052274999999</v>
+        <v>43.4674868</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1551217735132142</v>
+        <v>0.1574562836248448</v>
       </c>
       <c r="T57">
-        <v>1.843322155454943</v>
+        <v>1.882685349744707</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.214482010732125</v>
+        <v>2.174937689111908</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1064227647949317</v>
+        <v>0.106561981508917</v>
       </c>
       <c r="C58">
-        <v>350.9726681017465</v>
+        <v>339.6741501847184</v>
       </c>
       <c r="D58">
-        <v>832.8486681017466</v>
+        <v>831.3961501847185</v>
       </c>
       <c r="E58">
-        <v>478.4760000000001</v>
+        <v>488.3220000000001</v>
       </c>
       <c r="F58">
-        <v>551.3760000000001</v>
+        <v>561.2220000000001</v>
       </c>
       <c r="G58">
         <v>69.5</v>
@@ -6031,28 +6031,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M58">
-        <v>41.79430080000001</v>
+        <v>42.54062760000001</v>
       </c>
       <c r="N58">
-        <v>49.1056992</v>
+        <v>48.3593724</v>
       </c>
       <c r="O58">
-        <v>6.1382124</v>
+        <v>6.04492155</v>
       </c>
       <c r="P58">
-        <v>42.9674868</v>
+        <v>42.31445085</v>
       </c>
       <c r="Q58">
-        <v>43.4674868</v>
+        <v>42.81445085</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1574562836248448</v>
+        <v>0.1598993756021326</v>
       </c>
       <c r="T58">
-        <v>1.882685349744707</v>
+        <v>1.923879390280506</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.174937689111908</v>
+        <v>2.136780887548542</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.106561981508917</v>
+        <v>0.1067011982229023</v>
       </c>
       <c r="C59">
-        <v>339.6741501847184</v>
+        <v>328.3806899335178</v>
       </c>
       <c r="D59">
-        <v>831.3961501847185</v>
+        <v>829.9486899335179</v>
       </c>
       <c r="E59">
-        <v>488.3220000000001</v>
+        <v>498.1680000000001</v>
       </c>
       <c r="F59">
-        <v>561.2220000000001</v>
+        <v>571.0680000000001</v>
       </c>
       <c r="G59">
         <v>69.5</v>
@@ -6113,28 +6113,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M59">
-        <v>42.54062760000001</v>
+        <v>43.28695440000001</v>
       </c>
       <c r="N59">
-        <v>48.3593724</v>
+        <v>47.61304559999999</v>
       </c>
       <c r="O59">
-        <v>6.04492155</v>
+        <v>5.951630699999999</v>
       </c>
       <c r="P59">
-        <v>42.31445085</v>
+        <v>41.6614149</v>
       </c>
       <c r="Q59">
-        <v>42.81445085</v>
+        <v>42.1614149</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1598993756021326</v>
+        <v>0.1624588052926246</v>
       </c>
       <c r="T59">
-        <v>1.923879390280506</v>
+        <v>1.967035051794201</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.136780887548542</v>
+        <v>2.099939837763221</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1067011982229023</v>
+        <v>0.1068404149368876</v>
       </c>
       <c r="C60">
-        <v>328.3806899335179</v>
+        <v>317.0922609778758</v>
       </c>
       <c r="D60">
-        <v>829.9486899335179</v>
+        <v>828.5062609778757</v>
       </c>
       <c r="E60">
-        <v>498.168</v>
+        <v>508.014</v>
       </c>
       <c r="F60">
-        <v>571.068</v>
+        <v>580.914</v>
       </c>
       <c r="G60">
         <v>69.5</v>
@@ -6195,28 +6195,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M60">
-        <v>43.2869544</v>
+        <v>44.0332812</v>
       </c>
       <c r="N60">
-        <v>47.61304560000001</v>
+        <v>46.8667188</v>
       </c>
       <c r="O60">
-        <v>5.951630700000001</v>
+        <v>5.85833985</v>
       </c>
       <c r="P60">
-        <v>41.6614149</v>
+        <v>41.00837895</v>
       </c>
       <c r="Q60">
-        <v>42.1614149</v>
+        <v>41.50837895</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1624588052926246</v>
+        <v>0.165143085211921</v>
       </c>
       <c r="T60">
-        <v>1.967035051794201</v>
+        <v>2.012295867528076</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.099939837763222</v>
+        <v>2.064347637123167</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1068404149368876</v>
+        <v>0.106979631650873</v>
       </c>
       <c r="C61">
-        <v>317.0922609778758</v>
+        <v>305.8088371305263</v>
       </c>
       <c r="D61">
-        <v>828.5062609778757</v>
+        <v>827.0688371305263</v>
       </c>
       <c r="E61">
-        <v>508.014</v>
+        <v>517.86</v>
       </c>
       <c r="F61">
-        <v>580.914</v>
+        <v>590.76</v>
       </c>
       <c r="G61">
         <v>69.5</v>
@@ -6277,28 +6277,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M61">
-        <v>44.0332812</v>
+        <v>44.779608</v>
       </c>
       <c r="N61">
-        <v>46.8667188</v>
+        <v>46.120392</v>
       </c>
       <c r="O61">
-        <v>5.85833985</v>
+        <v>5.765049</v>
       </c>
       <c r="P61">
-        <v>41.00837895</v>
+        <v>40.355343</v>
       </c>
       <c r="Q61">
-        <v>41.50837895</v>
+        <v>40.855343</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.165143085211921</v>
+        <v>0.1679615791271823</v>
       </c>
       <c r="T61">
-        <v>2.012295867528076</v>
+        <v>2.059819724048644</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.064347637123167</v>
+        <v>2.029941843171115</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.106979631650873</v>
+        <v>0.1146980983648582</v>
       </c>
       <c r="C62">
-        <v>305.8088371305263</v>
+        <v>223.3882395668613</v>
       </c>
       <c r="D62">
-        <v>827.0688371305263</v>
+        <v>754.4942395668613</v>
       </c>
       <c r="E62">
-        <v>517.86</v>
+        <v>527.706</v>
       </c>
       <c r="F62">
-        <v>590.76</v>
+        <v>600.606</v>
       </c>
       <c r="G62">
         <v>69.5</v>
@@ -6359,45 +6359,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M62">
-        <v>44.779608</v>
+        <v>54.05454</v>
       </c>
       <c r="N62">
-        <v>46.120392</v>
+        <v>36.84546000000001</v>
       </c>
       <c r="O62">
-        <v>5.765049</v>
+        <v>4.605682500000001</v>
       </c>
       <c r="P62">
-        <v>40.355343</v>
+        <v>32.23977750000001</v>
       </c>
       <c r="Q62">
-        <v>40.855343</v>
+        <v>32.73977750000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1679615791271823</v>
+        <v>0.1709246111919442</v>
       </c>
       <c r="T62">
-        <v>2.059819724048644</v>
+        <v>2.109780701416422</v>
       </c>
       <c r="U62">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V62">
         <v>0.125</v>
       </c>
       <c r="W62">
-        <v>0.06632500000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.029941843171115</v>
+        <v>1.68163488210241</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1146980983648582</v>
+        <v>0.1149615650788436</v>
       </c>
       <c r="C63">
-        <v>223.3882395668613</v>
+        <v>211.2890655399415</v>
       </c>
       <c r="D63">
-        <v>754.4942395668613</v>
+        <v>752.2410655399415</v>
       </c>
       <c r="E63">
-        <v>527.706</v>
+        <v>537.552</v>
       </c>
       <c r="F63">
-        <v>600.606</v>
+        <v>610.452</v>
       </c>
       <c r="G63">
         <v>69.5</v>
@@ -6441,28 +6441,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M63">
-        <v>54.05454</v>
+        <v>54.94068</v>
       </c>
       <c r="N63">
-        <v>36.84546000000001</v>
+        <v>35.95932000000001</v>
       </c>
       <c r="O63">
-        <v>4.605682500000001</v>
+        <v>4.494915000000001</v>
       </c>
       <c r="P63">
-        <v>32.23977750000001</v>
+        <v>31.46440500000001</v>
       </c>
       <c r="Q63">
-        <v>32.73977750000001</v>
+        <v>31.96440500000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1709246111919442</v>
+        <v>0.1740435923127462</v>
       </c>
       <c r="T63">
-        <v>2.109780701416422</v>
+        <v>2.162371203908819</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.68163488210241</v>
+        <v>1.654511738842694</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1149615650788436</v>
+        <v>0.1152250317928289</v>
       </c>
       <c r="C64">
-        <v>211.2890655399415</v>
+        <v>199.2033089178371</v>
       </c>
       <c r="D64">
-        <v>752.2410655399415</v>
+        <v>750.0013089178372</v>
       </c>
       <c r="E64">
-        <v>537.552</v>
+        <v>547.398</v>
       </c>
       <c r="F64">
-        <v>610.452</v>
+        <v>620.298</v>
       </c>
       <c r="G64">
         <v>69.5</v>
@@ -6523,28 +6523,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M64">
-        <v>54.94068</v>
+        <v>55.82682</v>
       </c>
       <c r="N64">
-        <v>35.95932000000001</v>
+        <v>35.07318000000001</v>
       </c>
       <c r="O64">
-        <v>4.494915000000001</v>
+        <v>4.384147500000001</v>
       </c>
       <c r="P64">
-        <v>31.46440500000001</v>
+        <v>30.68903250000001</v>
       </c>
       <c r="Q64">
-        <v>31.96440500000001</v>
+        <v>31.18903250000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1740435923127462</v>
+        <v>0.1773311670076456</v>
       </c>
       <c r="T64">
-        <v>2.162371203908819</v>
+        <v>2.217804436265669</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.654511738842694</v>
+        <v>1.628249647749953</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1152250317928289</v>
+        <v>0.1154884985068142</v>
       </c>
       <c r="C65">
-        <v>199.2033089178371</v>
+        <v>187.1308502075655</v>
       </c>
       <c r="D65">
-        <v>750.0013089178372</v>
+        <v>747.7748502075655</v>
       </c>
       <c r="E65">
-        <v>547.398</v>
+        <v>557.244</v>
       </c>
       <c r="F65">
-        <v>620.298</v>
+        <v>630.144</v>
       </c>
       <c r="G65">
         <v>69.5</v>
@@ -6605,28 +6605,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M65">
-        <v>55.82682</v>
+        <v>56.71296</v>
       </c>
       <c r="N65">
-        <v>35.07318000000001</v>
+        <v>34.18704000000001</v>
       </c>
       <c r="O65">
-        <v>4.384147500000001</v>
+        <v>4.273380000000001</v>
       </c>
       <c r="P65">
-        <v>30.68903250000001</v>
+        <v>29.91366000000001</v>
       </c>
       <c r="Q65">
-        <v>31.18903250000001</v>
+        <v>30.41366000000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1773311670076456</v>
+        <v>0.1808013847411505</v>
       </c>
       <c r="T65">
-        <v>2.217804436265669</v>
+        <v>2.276317292642346</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.628249647749953</v>
+        <v>1.60280824700386</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1154884985068142</v>
+        <v>0.1157519652207995</v>
       </c>
       <c r="C66">
-        <v>187.1308502075655</v>
+        <v>175.0715713308545</v>
       </c>
       <c r="D66">
-        <v>747.7748502075655</v>
+        <v>745.5615713308545</v>
       </c>
       <c r="E66">
-        <v>557.244</v>
+        <v>567.09</v>
       </c>
       <c r="F66">
-        <v>630.144</v>
+        <v>639.99</v>
       </c>
       <c r="G66">
         <v>69.5</v>
@@ -6687,28 +6687,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M66">
-        <v>56.71296</v>
+        <v>57.5991</v>
       </c>
       <c r="N66">
-        <v>34.18704000000001</v>
+        <v>33.30090000000001</v>
       </c>
       <c r="O66">
-        <v>4.273380000000001</v>
+        <v>4.162612500000001</v>
       </c>
       <c r="P66">
-        <v>29.91366000000001</v>
+        <v>29.1382875</v>
       </c>
       <c r="Q66">
-        <v>30.41366000000001</v>
+        <v>29.6382875</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1808013847411505</v>
+        <v>0.1844699006308556</v>
       </c>
       <c r="T66">
-        <v>2.276317292642346</v>
+        <v>2.338173740811975</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.60280824700386</v>
+        <v>1.578149658588416</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1157519652207995</v>
+        <v>0.1160154319347848</v>
       </c>
       <c r="C67">
-        <v>175.0715713308545</v>
+        <v>163.0253556032685</v>
       </c>
       <c r="D67">
-        <v>745.5615713308545</v>
+        <v>743.3613556032685</v>
       </c>
       <c r="E67">
-        <v>567.09</v>
+        <v>576.936</v>
       </c>
       <c r="F67">
-        <v>639.99</v>
+        <v>649.836</v>
       </c>
       <c r="G67">
         <v>69.5</v>
@@ -6769,28 +6769,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M67">
-        <v>57.5991</v>
+        <v>58.48524</v>
       </c>
       <c r="N67">
-        <v>33.30090000000001</v>
+        <v>32.41476000000001</v>
       </c>
       <c r="O67">
-        <v>4.162612500000001</v>
+        <v>4.051845000000001</v>
       </c>
       <c r="P67">
-        <v>29.1382875</v>
+        <v>28.36291500000001</v>
       </c>
       <c r="Q67">
-        <v>29.6382875</v>
+        <v>28.86291500000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1844699006308556</v>
+        <v>0.1883542115728964</v>
       </c>
       <c r="T67">
-        <v>2.338173740811975</v>
+        <v>2.403668803579817</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.578149658588416</v>
+        <v>1.554238300124955</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1160154319347848</v>
+        <v>0.1162788986487701</v>
       </c>
       <c r="C68">
-        <v>163.0253556032685</v>
+        <v>150.9920877137017</v>
       </c>
       <c r="D68">
-        <v>743.3613556032685</v>
+        <v>741.1740877137017</v>
       </c>
       <c r="E68">
-        <v>576.936</v>
+        <v>586.782</v>
       </c>
       <c r="F68">
-        <v>649.836</v>
+        <v>659.682</v>
       </c>
       <c r="G68">
         <v>69.5</v>
@@ -6851,28 +6851,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M68">
-        <v>58.48524</v>
+        <v>59.37138</v>
       </c>
       <c r="N68">
-        <v>32.41476000000001</v>
+        <v>31.52862</v>
       </c>
       <c r="O68">
-        <v>4.051845000000001</v>
+        <v>3.9410775</v>
       </c>
       <c r="P68">
-        <v>28.36291500000001</v>
+        <v>27.5875425</v>
       </c>
       <c r="Q68">
-        <v>28.86291500000001</v>
+        <v>28.0875425</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1883542115728964</v>
+        <v>0.1924739352993033</v>
       </c>
       <c r="T68">
-        <v>2.403668803579817</v>
+        <v>2.473133264091165</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.554238300124955</v>
+        <v>1.531040713555925</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1162788986487701</v>
+        <v>0.1165423653627554</v>
       </c>
       <c r="C69">
-        <v>150.9920877137017</v>
+        <v>138.9716537042334</v>
       </c>
       <c r="D69">
-        <v>741.1740877137017</v>
+        <v>738.9996537042334</v>
       </c>
       <c r="E69">
-        <v>586.782</v>
+        <v>596.628</v>
       </c>
       <c r="F69">
-        <v>659.682</v>
+        <v>669.528</v>
       </c>
       <c r="G69">
         <v>69.5</v>
@@ -6933,28 +6933,28 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M69">
-        <v>59.37138</v>
+        <v>60.25752</v>
       </c>
       <c r="N69">
-        <v>31.52862</v>
+        <v>30.64248000000001</v>
       </c>
       <c r="O69">
-        <v>3.9410775</v>
+        <v>3.830310000000001</v>
       </c>
       <c r="P69">
-        <v>27.5875425</v>
+        <v>26.81217000000001</v>
       </c>
       <c r="Q69">
-        <v>28.0875425</v>
+        <v>27.31217000000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1924739352993033</v>
+        <v>0.1968511417586106</v>
       </c>
       <c r="T69">
-        <v>2.473133264091165</v>
+        <v>2.546939253384473</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.531040713555925</v>
+        <v>1.508525408944809</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1165423653627554</v>
+        <v>0.1526236104857081</v>
       </c>
       <c r="C70">
-        <v>138.9716537042334</v>
+        <v>-82.68510620602319</v>
       </c>
       <c r="D70">
-        <v>738.9996537042334</v>
+        <v>527.1888937939768</v>
       </c>
       <c r="E70">
-        <v>596.628</v>
+        <v>606.474</v>
       </c>
       <c r="F70">
-        <v>669.528</v>
+        <v>679.374</v>
       </c>
       <c r="G70">
         <v>69.5</v>
@@ -7015,45 +7015,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M70">
-        <v>60.25752</v>
+        <v>99.73210320000001</v>
       </c>
       <c r="N70">
-        <v>30.64248000000001</v>
+        <v>-8.832103200000006</v>
       </c>
       <c r="O70">
-        <v>3.830310000000001</v>
+        <v>-1.104012900000001</v>
       </c>
       <c r="P70">
-        <v>26.81217000000001</v>
+        <v>-7.728090300000005</v>
       </c>
       <c r="Q70">
-        <v>27.31217000000001</v>
+        <v>-7.228090300000005</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1968511417586106</v>
+        <v>0.2028123544004383</v>
       </c>
       <c r="T70">
-        <v>2.546939253384473</v>
+        <v>2.647453862532584</v>
       </c>
       <c r="U70">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.125</v>
+        <v>0.1139302154012932</v>
       </c>
       <c r="W70">
-        <v>0.07875</v>
+        <v>0.1300750443790902</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.508525408944809</v>
+        <v>0.9114417232103453</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1526236104857081</v>
+        <v>0.1536336104857081</v>
       </c>
       <c r="C71">
-        <v>-82.68510620602319</v>
+        <v>-96.7271440608672</v>
       </c>
       <c r="D71">
-        <v>527.1888937939768</v>
+        <v>522.9928559391328</v>
       </c>
       <c r="E71">
-        <v>606.474</v>
+        <v>616.3200000000001</v>
       </c>
       <c r="F71">
-        <v>679.374</v>
+        <v>689.22</v>
       </c>
       <c r="G71">
         <v>69.5</v>
@@ -7097,37 +7097,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M71">
-        <v>99.73210320000001</v>
+        <v>101.177496</v>
       </c>
       <c r="N71">
-        <v>-8.832103200000006</v>
+        <v>-10.27749600000001</v>
       </c>
       <c r="O71">
-        <v>-1.104012900000001</v>
+        <v>-1.284687000000002</v>
       </c>
       <c r="P71">
-        <v>-7.728090300000005</v>
+        <v>-8.992809000000012</v>
       </c>
       <c r="Q71">
-        <v>-7.228090300000005</v>
+        <v>-8.492809000000012</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2028123544004383</v>
+        <v>0.2080460995471195</v>
       </c>
       <c r="T71">
-        <v>2.647453862532584</v>
+        <v>2.735702324617002</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1139302154012932</v>
+        <v>0.1123026408955604</v>
       </c>
       <c r="W71">
-        <v>0.1300750443790902</v>
+        <v>0.1303139723165317</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9114417232103453</v>
+        <v>0.8984211271644832</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1536336104857081</v>
+        <v>0.1546436104857081</v>
       </c>
       <c r="C72">
-        <v>-96.7271440608672</v>
+        <v>-110.7029145730355</v>
       </c>
       <c r="D72">
-        <v>522.9928559391328</v>
+        <v>518.8630854269646</v>
       </c>
       <c r="E72">
-        <v>616.3200000000001</v>
+        <v>626.1660000000002</v>
       </c>
       <c r="F72">
-        <v>689.22</v>
+        <v>699.0660000000001</v>
       </c>
       <c r="G72">
         <v>69.5</v>
@@ -7179,37 +7179,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M72">
-        <v>101.177496</v>
+        <v>102.6228888</v>
       </c>
       <c r="N72">
-        <v>-10.27749600000001</v>
+        <v>-11.72288880000002</v>
       </c>
       <c r="O72">
-        <v>-1.284687000000002</v>
+        <v>-1.465361100000003</v>
       </c>
       <c r="P72">
-        <v>-8.992809000000012</v>
+        <v>-10.25752770000002</v>
       </c>
       <c r="Q72">
-        <v>-8.492809000000012</v>
+        <v>-9.757527700000018</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2080460995471195</v>
+        <v>0.2136407926349513</v>
       </c>
       <c r="T72">
-        <v>2.735702324617002</v>
+        <v>2.830036887534831</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1123026408955604</v>
+        <v>0.1107209135590032</v>
       </c>
       <c r="W72">
-        <v>0.1303139723165317</v>
+        <v>0.1305461698895383</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8984211271644832</v>
+        <v>0.8857673084720256</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1546436104857081</v>
+        <v>0.1556536104857081</v>
       </c>
       <c r="C73">
-        <v>-110.7029145730354</v>
+        <v>-124.6139752676871</v>
       </c>
       <c r="D73">
-        <v>518.8630854269646</v>
+        <v>514.7980247323129</v>
       </c>
       <c r="E73">
-        <v>626.1660000000001</v>
+        <v>636.0120000000001</v>
       </c>
       <c r="F73">
-        <v>699.066</v>
+        <v>708.912</v>
       </c>
       <c r="G73">
         <v>69.5</v>
@@ -7261,37 +7261,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M73">
-        <v>102.6228888</v>
+        <v>104.0682816</v>
       </c>
       <c r="N73">
-        <v>-11.72288880000001</v>
+        <v>-13.16828160000001</v>
       </c>
       <c r="O73">
-        <v>-1.465361100000001</v>
+        <v>-1.646035200000002</v>
       </c>
       <c r="P73">
-        <v>-10.25752770000001</v>
+        <v>-11.52224640000001</v>
       </c>
       <c r="Q73">
-        <v>-9.757527700000006</v>
+        <v>-11.02224640000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2136407926349512</v>
+        <v>0.2196351066576281</v>
       </c>
       <c r="T73">
-        <v>2.830036887534829</v>
+        <v>2.931109633518217</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1107209135590032</v>
+        <v>0.1091831230929059</v>
       </c>
       <c r="W73">
-        <v>0.1305461698895383</v>
+        <v>0.1307719175299614</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8857673084720257</v>
+        <v>0.8734649847432475</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1556536104857081</v>
+        <v>0.1566636104857081</v>
       </c>
       <c r="C74">
-        <v>-124.6139752676871</v>
+        <v>-138.461835239357</v>
       </c>
       <c r="D74">
-        <v>514.7980247323129</v>
+        <v>510.796164760643</v>
       </c>
       <c r="E74">
-        <v>636.0120000000001</v>
+        <v>645.8580000000001</v>
       </c>
       <c r="F74">
-        <v>708.912</v>
+        <v>718.758</v>
       </c>
       <c r="G74">
         <v>69.5</v>
@@ -7343,37 +7343,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M74">
-        <v>104.0682816</v>
+        <v>105.5136744</v>
       </c>
       <c r="N74">
-        <v>-13.16828160000001</v>
+        <v>-14.61367440000001</v>
       </c>
       <c r="O74">
-        <v>-1.646035200000002</v>
+        <v>-1.826709300000001</v>
       </c>
       <c r="P74">
-        <v>-11.52224640000001</v>
+        <v>-12.78696510000001</v>
       </c>
       <c r="Q74">
-        <v>-11.02224640000001</v>
+        <v>-12.28696510000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2196351066576281</v>
+        <v>0.2260734439412439</v>
       </c>
       <c r="T74">
-        <v>2.931109633518217</v>
+        <v>3.039669249574446</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1091831230929059</v>
+        <v>0.1076874638724552</v>
       </c>
       <c r="W74">
-        <v>0.1307719175299614</v>
+        <v>0.1309914803035236</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8734649847432475</v>
+        <v>0.8614997109796414</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1566636104857081</v>
+        <v>0.1576736104857081</v>
       </c>
       <c r="C75">
-        <v>-138.461835239357</v>
+        <v>-152.2479570198477</v>
       </c>
       <c r="D75">
-        <v>510.796164760643</v>
+        <v>506.8560429801524</v>
       </c>
       <c r="E75">
-        <v>645.8580000000001</v>
+        <v>655.7040000000001</v>
       </c>
       <c r="F75">
-        <v>718.758</v>
+        <v>728.604</v>
       </c>
       <c r="G75">
         <v>69.5</v>
@@ -7425,37 +7425,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M75">
-        <v>105.5136744</v>
+        <v>106.9590672</v>
       </c>
       <c r="N75">
-        <v>-14.61367440000001</v>
+        <v>-16.05906720000002</v>
       </c>
       <c r="O75">
-        <v>-1.826709300000001</v>
+        <v>-2.007383400000002</v>
       </c>
       <c r="P75">
-        <v>-12.78696510000001</v>
+        <v>-14.05168380000001</v>
       </c>
       <c r="Q75">
-        <v>-12.28696510000001</v>
+        <v>-13.55168380000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2260734439412439</v>
+        <v>0.233007037938984</v>
       </c>
       <c r="T75">
-        <v>3.039669249574446</v>
+        <v>3.15657960532731</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1076874638724552</v>
+        <v>0.1062322278741788</v>
       </c>
       <c r="W75">
-        <v>0.1309914803035236</v>
+        <v>0.1312051089480706</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8614997109796414</v>
+        <v>0.84985782299343</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1576736104857081</v>
+        <v>0.1586836104857081</v>
       </c>
       <c r="C76">
-        <v>-152.2479570198477</v>
+        <v>-165.9737583603342</v>
       </c>
       <c r="D76">
-        <v>506.8560429801524</v>
+        <v>502.9762416396658</v>
       </c>
       <c r="E76">
-        <v>655.7040000000001</v>
+        <v>665.5500000000001</v>
       </c>
       <c r="F76">
-        <v>728.604</v>
+        <v>738.45</v>
       </c>
       <c r="G76">
         <v>69.5</v>
@@ -7507,37 +7507,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M76">
-        <v>106.9590672</v>
+        <v>108.40446</v>
       </c>
       <c r="N76">
-        <v>-16.05906720000002</v>
+        <v>-17.50446000000001</v>
       </c>
       <c r="O76">
-        <v>-2.007383400000002</v>
+        <v>-2.188057500000001</v>
       </c>
       <c r="P76">
-        <v>-14.05168380000001</v>
+        <v>-15.31640250000001</v>
       </c>
       <c r="Q76">
-        <v>-13.55168380000001</v>
+        <v>-14.81640250000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.233007037938984</v>
+        <v>0.2404953194565434</v>
       </c>
       <c r="T76">
-        <v>3.15657960532731</v>
+        <v>3.282842789540402</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1062322278741788</v>
+        <v>0.1048157981691897</v>
       </c>
       <c r="W76">
-        <v>0.1312051089480706</v>
+        <v>0.131413040828763</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.84985782299343</v>
+        <v>0.8385263853535176</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1586836104857081</v>
+        <v>0.1596936104857081</v>
       </c>
       <c r="C77">
-        <v>-165.9737583603342</v>
+        <v>-179.6406139322438</v>
       </c>
       <c r="D77">
-        <v>502.9762416396658</v>
+        <v>499.1553860677562</v>
       </c>
       <c r="E77">
-        <v>665.5500000000001</v>
+        <v>675.3960000000001</v>
       </c>
       <c r="F77">
-        <v>738.45</v>
+        <v>748.296</v>
       </c>
       <c r="G77">
         <v>69.5</v>
@@ -7589,37 +7589,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M77">
-        <v>108.40446</v>
+        <v>109.8498528</v>
       </c>
       <c r="N77">
-        <v>-17.50446000000001</v>
+        <v>-18.94985280000002</v>
       </c>
       <c r="O77">
-        <v>-2.188057500000001</v>
+        <v>-2.368731600000002</v>
       </c>
       <c r="P77">
-        <v>-15.31640250000001</v>
+        <v>-16.58112120000001</v>
       </c>
       <c r="Q77">
-        <v>-14.81640250000001</v>
+        <v>-16.08112120000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2404953194565434</v>
+        <v>0.2486076244338994</v>
       </c>
       <c r="T77">
-        <v>3.282842789540402</v>
+        <v>3.419627905771252</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1048157981691897</v>
+        <v>0.1034366429301214</v>
       </c>
       <c r="W77">
-        <v>0.131413040828763</v>
+        <v>0.1316155008178582</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8385263853535176</v>
+        <v>0.8274931434409714</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1596936104857081</v>
+        <v>0.1607036104857081</v>
       </c>
       <c r="C78">
-        <v>-179.6406139322438</v>
+        <v>-193.249856951194</v>
       </c>
       <c r="D78">
-        <v>499.1553860677562</v>
+        <v>495.392143048806</v>
       </c>
       <c r="E78">
-        <v>675.3960000000001</v>
+        <v>685.2420000000001</v>
       </c>
       <c r="F78">
-        <v>748.296</v>
+        <v>758.1420000000001</v>
       </c>
       <c r="G78">
         <v>69.5</v>
@@ -7671,37 +7671,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M78">
-        <v>109.8498528</v>
+        <v>111.2952456</v>
       </c>
       <c r="N78">
-        <v>-18.94985280000002</v>
+        <v>-20.39524560000001</v>
       </c>
       <c r="O78">
-        <v>-2.368731600000002</v>
+        <v>-2.549405700000001</v>
       </c>
       <c r="P78">
-        <v>-16.58112120000001</v>
+        <v>-17.84583990000001</v>
       </c>
       <c r="Q78">
-        <v>-16.08112120000001</v>
+        <v>-17.34583990000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2486076244338994</v>
+        <v>0.2574253472353732</v>
       </c>
       <c r="T78">
-        <v>3.419627905771252</v>
+        <v>3.56830737993522</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1034366429301214</v>
+        <v>0.1020933099050549</v>
       </c>
       <c r="W78">
-        <v>0.1316155008178582</v>
+        <v>0.131812702105938</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8274931434409714</v>
+        <v>0.8167464792404393</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1607036104857081</v>
+        <v>0.1617136104857081</v>
       </c>
       <c r="C79">
-        <v>-193.249856951194</v>
+        <v>-206.8027807280218</v>
       </c>
       <c r="D79">
-        <v>495.392143048806</v>
+        <v>491.6852192719782</v>
       </c>
       <c r="E79">
-        <v>685.2420000000001</v>
+        <v>695.0880000000001</v>
       </c>
       <c r="F79">
-        <v>758.1420000000001</v>
+        <v>767.9880000000001</v>
       </c>
       <c r="G79">
         <v>69.5</v>
@@ -7753,37 +7753,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M79">
-        <v>111.2952456</v>
+        <v>112.7406384</v>
       </c>
       <c r="N79">
-        <v>-20.39524560000001</v>
+        <v>-21.84063840000002</v>
       </c>
       <c r="O79">
-        <v>-2.549405700000001</v>
+        <v>-2.730079800000002</v>
       </c>
       <c r="P79">
-        <v>-17.84583990000001</v>
+        <v>-19.11055860000002</v>
       </c>
       <c r="Q79">
-        <v>-17.34583990000001</v>
+        <v>-18.61055860000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2574253472353732</v>
+        <v>0.2670446812006175</v>
       </c>
       <c r="T79">
-        <v>3.56830737993522</v>
+        <v>3.730503169932276</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1020933099050549</v>
+        <v>0.1007844213165286</v>
       </c>
       <c r="W79">
-        <v>0.131812702105938</v>
+        <v>0.1320048469507336</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8167464792404393</v>
+        <v>0.8062753705322285</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1617136104857081</v>
+        <v>0.2065003990473187</v>
       </c>
       <c r="C80">
-        <v>-206.8027807280218</v>
+        <v>-339.149057509777</v>
       </c>
       <c r="D80">
-        <v>491.6852192719782</v>
+        <v>369.184942490223</v>
       </c>
       <c r="E80">
-        <v>695.0880000000001</v>
+        <v>704.9340000000001</v>
       </c>
       <c r="F80">
-        <v>767.9880000000001</v>
+        <v>777.8340000000001</v>
       </c>
       <c r="G80">
         <v>69.5</v>
@@ -7835,45 +7835,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M80">
-        <v>112.7406384</v>
+        <v>156.1890672</v>
       </c>
       <c r="N80">
-        <v>-21.84063840000002</v>
+        <v>-65.28906720000001</v>
       </c>
       <c r="O80">
-        <v>-2.730079800000002</v>
+        <v>-8.161133400000001</v>
       </c>
       <c r="P80">
-        <v>-19.11055860000002</v>
+        <v>-57.12793380000001</v>
       </c>
       <c r="Q80">
-        <v>-18.61055860000002</v>
+        <v>-56.62793380000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2670446812006175</v>
+        <v>0.2828981829797451</v>
       </c>
       <c r="T80">
-        <v>3.730503169932276</v>
+        <v>3.997815985411599</v>
       </c>
       <c r="U80">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1007844213165286</v>
+        <v>0.07274836967590265</v>
       </c>
       <c r="W80">
-        <v>0.1320048469507336</v>
+        <v>0.1861921273690788</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.8062753705322285</v>
+        <v>0.5819869574072212</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2065003990473187</v>
+        <v>0.2080503990473187</v>
       </c>
       <c r="C81">
-        <v>-339.149057509777</v>
+        <v>-352.1511304613275</v>
       </c>
       <c r="D81">
-        <v>369.184942490223</v>
+        <v>366.0288695386726</v>
       </c>
       <c r="E81">
-        <v>704.9340000000001</v>
+        <v>714.7800000000001</v>
       </c>
       <c r="F81">
-        <v>777.8340000000001</v>
+        <v>787.6800000000001</v>
       </c>
       <c r="G81">
         <v>69.5</v>
@@ -7917,37 +7917,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M81">
-        <v>156.1890672</v>
+        <v>158.166144</v>
       </c>
       <c r="N81">
-        <v>-65.28906720000001</v>
+        <v>-67.26614400000003</v>
       </c>
       <c r="O81">
-        <v>-8.161133400000001</v>
+        <v>-8.408268000000003</v>
       </c>
       <c r="P81">
-        <v>-57.12793380000001</v>
+        <v>-58.85787600000002</v>
       </c>
       <c r="Q81">
-        <v>-56.62793380000001</v>
+        <v>-58.35787600000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2828981829797451</v>
+        <v>0.2947530921287324</v>
       </c>
       <c r="T81">
-        <v>3.997815985411599</v>
+        <v>4.197706784682179</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07274836967590265</v>
+        <v>0.07183901505495385</v>
       </c>
       <c r="W81">
-        <v>0.1861921273690788</v>
+        <v>0.1863747257769653</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5819869574072212</v>
+        <v>0.5747121204396308</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2080503990473187</v>
+        <v>0.2096003990473187</v>
       </c>
       <c r="C82">
-        <v>-352.1511304613275</v>
+        <v>-365.0996997908624</v>
       </c>
       <c r="D82">
-        <v>366.0288695386726</v>
+        <v>362.9263002091377</v>
       </c>
       <c r="E82">
-        <v>714.7800000000001</v>
+        <v>724.6260000000001</v>
       </c>
       <c r="F82">
-        <v>787.6800000000001</v>
+        <v>797.5260000000001</v>
       </c>
       <c r="G82">
         <v>69.5</v>
@@ -7999,37 +7999,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M82">
-        <v>158.166144</v>
+        <v>160.1432208</v>
       </c>
       <c r="N82">
-        <v>-67.26614400000003</v>
+        <v>-69.24322080000002</v>
       </c>
       <c r="O82">
-        <v>-8.408268000000003</v>
+        <v>-8.655402600000002</v>
       </c>
       <c r="P82">
-        <v>-58.85787600000002</v>
+        <v>-60.58781820000002</v>
       </c>
       <c r="Q82">
-        <v>-58.35787600000002</v>
+        <v>-60.08781820000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2947530921287324</v>
+        <v>0.3078558864512971</v>
       </c>
       <c r="T82">
-        <v>4.197706784682179</v>
+        <v>4.418638720718082</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.07183901505495385</v>
+        <v>0.07095211363452232</v>
       </c>
       <c r="W82">
-        <v>0.1863747257769653</v>
+        <v>0.1865528155821879</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5747121204396308</v>
+        <v>0.5676169090761787</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2096003990473187</v>
+        <v>0.2111503990473187</v>
       </c>
       <c r="C83">
-        <v>-365.0996997908624</v>
+        <v>-377.9961146007279</v>
       </c>
       <c r="D83">
-        <v>362.9263002091377</v>
+        <v>359.8758853992722</v>
       </c>
       <c r="E83">
-        <v>724.6260000000001</v>
+        <v>734.4720000000001</v>
       </c>
       <c r="F83">
-        <v>797.5260000000001</v>
+        <v>807.3720000000001</v>
       </c>
       <c r="G83">
         <v>69.5</v>
@@ -8081,37 +8081,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M83">
-        <v>160.1432208</v>
+        <v>162.1202976</v>
       </c>
       <c r="N83">
-        <v>-69.24322080000002</v>
+        <v>-71.22029760000001</v>
       </c>
       <c r="O83">
-        <v>-8.655402600000002</v>
+        <v>-8.902537200000001</v>
       </c>
       <c r="P83">
-        <v>-60.58781820000002</v>
+        <v>-62.31776040000001</v>
       </c>
       <c r="Q83">
-        <v>-60.08781820000002</v>
+        <v>-61.81776040000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3078558864512971</v>
+        <v>0.3224145468097026</v>
       </c>
       <c r="T83">
-        <v>4.418638720718082</v>
+        <v>4.664118649646865</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.07095211363452232</v>
+        <v>0.07008684395605254</v>
       </c>
       <c r="W83">
-        <v>0.1865528155821879</v>
+        <v>0.1867265617336246</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5676169090761787</v>
+        <v>0.5606947516484204</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2111503990473187</v>
+        <v>0.2127003990473187</v>
       </c>
       <c r="C84">
-        <v>-377.9961146007279</v>
+        <v>-390.8416790142134</v>
       </c>
       <c r="D84">
-        <v>359.8758853992722</v>
+        <v>356.8763209857867</v>
       </c>
       <c r="E84">
-        <v>734.4720000000001</v>
+        <v>744.3180000000001</v>
       </c>
       <c r="F84">
-        <v>807.3720000000001</v>
+        <v>817.2180000000001</v>
       </c>
       <c r="G84">
         <v>69.5</v>
@@ -8163,37 +8163,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M84">
-        <v>162.1202976</v>
+        <v>164.0973744</v>
       </c>
       <c r="N84">
-        <v>-71.22029760000001</v>
+        <v>-73.1973744</v>
       </c>
       <c r="O84">
-        <v>-8.902537200000001</v>
+        <v>-9.1496718</v>
       </c>
       <c r="P84">
-        <v>-62.31776040000001</v>
+        <v>-64.04770260000001</v>
       </c>
       <c r="Q84">
-        <v>-61.81776040000001</v>
+        <v>-63.54770260000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3224145468097026</v>
+        <v>0.3386859907396851</v>
       </c>
       <c r="T84">
-        <v>4.664118649646865</v>
+        <v>4.938478570214328</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.07008684395605254</v>
+        <v>0.06924242414935312</v>
       </c>
       <c r="W84">
-        <v>0.1867265617336246</v>
+        <v>0.1868961212308099</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5606947516484204</v>
+        <v>0.5539393931948249</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2127003990473187</v>
+        <v>0.2142503990473187</v>
       </c>
       <c r="C85">
-        <v>-390.8416790142134</v>
+        <v>-403.63765403456</v>
       </c>
       <c r="D85">
-        <v>356.8763209857867</v>
+        <v>353.9263459654401</v>
       </c>
       <c r="E85">
-        <v>744.3180000000001</v>
+        <v>754.1640000000001</v>
       </c>
       <c r="F85">
-        <v>817.2180000000001</v>
+        <v>827.0640000000001</v>
       </c>
       <c r="G85">
         <v>69.5</v>
@@ -8245,37 +8245,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M85">
-        <v>164.0973744</v>
+        <v>166.0744512</v>
       </c>
       <c r="N85">
-        <v>-73.1973744</v>
+        <v>-75.17445120000002</v>
       </c>
       <c r="O85">
-        <v>-9.1496718</v>
+        <v>-9.396806400000003</v>
       </c>
       <c r="P85">
-        <v>-64.04770260000001</v>
+        <v>-65.77764480000002</v>
       </c>
       <c r="Q85">
-        <v>-63.54770260000001</v>
+        <v>-65.27764480000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3386859907396851</v>
+        <v>0.3569913651609156</v>
       </c>
       <c r="T85">
-        <v>4.938478570214328</v>
+        <v>5.247133480852725</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.06924242414935312</v>
+        <v>0.06841810957614652</v>
       </c>
       <c r="W85">
-        <v>0.1868961212308099</v>
+        <v>0.1870616435971098</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5539393931948249</v>
+        <v>0.5473448766091722</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2142503990473187</v>
+        <v>0.2158003990473186</v>
       </c>
       <c r="C86">
-        <v>-403.6376540345598</v>
+        <v>-416.3852593125206</v>
       </c>
       <c r="D86">
-        <v>353.9263459654402</v>
+        <v>351.0247406874793</v>
       </c>
       <c r="E86">
-        <v>754.164</v>
+        <v>764.01</v>
       </c>
       <c r="F86">
-        <v>827.064</v>
+        <v>836.91</v>
       </c>
       <c r="G86">
         <v>69.5</v>
@@ -8327,37 +8327,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M86">
-        <v>166.0744512</v>
+        <v>168.051528</v>
       </c>
       <c r="N86">
-        <v>-75.17445119999999</v>
+        <v>-77.15152799999998</v>
       </c>
       <c r="O86">
-        <v>-9.396806399999999</v>
+        <v>-9.643940999999998</v>
       </c>
       <c r="P86">
-        <v>-65.77764479999999</v>
+        <v>-67.50758699999999</v>
       </c>
       <c r="Q86">
-        <v>-65.27764479999999</v>
+        <v>-67.00758699999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3569913651609153</v>
+        <v>0.3777374561716429</v>
       </c>
       <c r="T86">
-        <v>5.247133480852721</v>
+        <v>5.596942379576236</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.06841810957614654</v>
+        <v>0.06761319063995658</v>
       </c>
       <c r="W86">
-        <v>0.1870616435971098</v>
+        <v>0.1872232713194967</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5473448766091723</v>
+        <v>0.5409055251196526</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2158003990473186</v>
+        <v>0.2173503990473187</v>
       </c>
       <c r="C87">
-        <v>-416.3852593125206</v>
+        <v>-429.0856748276857</v>
       </c>
       <c r="D87">
-        <v>351.0247406874793</v>
+        <v>348.1703251723143</v>
       </c>
       <c r="E87">
-        <v>764.01</v>
+        <v>773.856</v>
       </c>
       <c r="F87">
-        <v>836.91</v>
+        <v>846.756</v>
       </c>
       <c r="G87">
         <v>69.5</v>
@@ -8409,37 +8409,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M87">
-        <v>168.051528</v>
+        <v>170.0286048</v>
       </c>
       <c r="N87">
-        <v>-77.15152799999998</v>
+        <v>-79.12860480000001</v>
       </c>
       <c r="O87">
-        <v>-9.643940999999998</v>
+        <v>-9.891075600000001</v>
       </c>
       <c r="P87">
-        <v>-67.50758699999999</v>
+        <v>-69.23752920000001</v>
       </c>
       <c r="Q87">
-        <v>-67.00758699999999</v>
+        <v>-68.73752920000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3777374561716429</v>
+        <v>0.4014472744696175</v>
       </c>
       <c r="T87">
-        <v>5.596942379576236</v>
+        <v>5.996723978117396</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.06761319063995658</v>
+        <v>0.06682699074879429</v>
       </c>
       <c r="W87">
-        <v>0.1872232713194967</v>
+        <v>0.1873811402576421</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5409055251196526</v>
+        <v>0.5346159259903542</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2173503990473187</v>
+        <v>0.2189003990473186</v>
       </c>
       <c r="C88">
-        <v>-429.0856748276857</v>
+        <v>-441.7400424884324</v>
       </c>
       <c r="D88">
-        <v>348.1703251723143</v>
+        <v>345.3619575115676</v>
       </c>
       <c r="E88">
-        <v>773.856</v>
+        <v>783.702</v>
       </c>
       <c r="F88">
-        <v>846.756</v>
+        <v>856.602</v>
       </c>
       <c r="G88">
         <v>69.5</v>
@@ -8491,37 +8491,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M88">
-        <v>170.0286048</v>
+        <v>172.0056816</v>
       </c>
       <c r="N88">
-        <v>-79.12860480000001</v>
+        <v>-81.1056816</v>
       </c>
       <c r="O88">
-        <v>-9.891075600000001</v>
+        <v>-10.1382102</v>
       </c>
       <c r="P88">
-        <v>-69.23752920000001</v>
+        <v>-70.96747139999999</v>
       </c>
       <c r="Q88">
-        <v>-68.73752920000001</v>
+        <v>-70.46747139999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4014472744696175</v>
+        <v>0.4288047571211265</v>
       </c>
       <c r="T88">
-        <v>5.996723978117396</v>
+        <v>6.45801043797258</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.06682699074879429</v>
+        <v>0.06605886441834838</v>
       </c>
       <c r="W88">
-        <v>0.1873811402576421</v>
+        <v>0.1875353800247956</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5346159259903542</v>
+        <v>0.528470915346787</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2189003990473186</v>
+        <v>0.2204503990473187</v>
       </c>
       <c r="C89">
-        <v>-441.7400424884324</v>
+        <v>-454.3494676550679</v>
       </c>
       <c r="D89">
-        <v>345.3619575115676</v>
+        <v>342.598532344932</v>
       </c>
       <c r="E89">
-        <v>783.702</v>
+        <v>793.548</v>
       </c>
       <c r="F89">
-        <v>856.602</v>
+        <v>866.448</v>
       </c>
       <c r="G89">
         <v>69.5</v>
@@ -8573,37 +8573,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M89">
-        <v>172.0056816</v>
+        <v>173.9827584</v>
       </c>
       <c r="N89">
-        <v>-81.1056816</v>
+        <v>-83.08275839999999</v>
       </c>
       <c r="O89">
-        <v>-10.1382102</v>
+        <v>-10.3853448</v>
       </c>
       <c r="P89">
-        <v>-70.96747139999999</v>
+        <v>-72.69741359999999</v>
       </c>
       <c r="Q89">
-        <v>-70.46747139999999</v>
+        <v>-72.19741359999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4288047571211265</v>
+        <v>0.4607218202145538</v>
       </c>
       <c r="T89">
-        <v>6.45801043797258</v>
+        <v>6.996177974470296</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.06605886441834838</v>
+        <v>0.06530819550450351</v>
       </c>
       <c r="W89">
-        <v>0.1875353800247956</v>
+        <v>0.1876861143426957</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.528470915346787</v>
+        <v>0.5224655640360281</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2204503990473187</v>
+        <v>0.2220003990473187</v>
       </c>
       <c r="C90">
-        <v>-454.3494676550679</v>
+        <v>-466.9150205904238</v>
       </c>
       <c r="D90">
-        <v>342.598532344932</v>
+        <v>339.8789794095762</v>
       </c>
       <c r="E90">
-        <v>793.548</v>
+        <v>803.394</v>
       </c>
       <c r="F90">
-        <v>866.448</v>
+        <v>876.294</v>
       </c>
       <c r="G90">
         <v>69.5</v>
@@ -8655,37 +8655,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M90">
-        <v>173.9827584</v>
+        <v>175.9598352</v>
       </c>
       <c r="N90">
-        <v>-83.08275839999999</v>
+        <v>-85.05983520000001</v>
       </c>
       <c r="O90">
-        <v>-10.3853448</v>
+        <v>-10.6324794</v>
       </c>
       <c r="P90">
-        <v>-72.69741359999999</v>
+        <v>-74.42735580000002</v>
       </c>
       <c r="Q90">
-        <v>-72.19741359999999</v>
+        <v>-73.92735580000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4607218202145538</v>
+        <v>0.4984419856886042</v>
       </c>
       <c r="T90">
-        <v>6.996177974470296</v>
+        <v>7.632194153967597</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.06530819550450351</v>
+        <v>0.06457439555501471</v>
       </c>
       <c r="W90">
-        <v>0.1876861143426957</v>
+        <v>0.1878334613725531</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5224655640360281</v>
+        <v>0.5165951644401177</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2220003990473187</v>
+        <v>0.2235503990473187</v>
       </c>
       <c r="C91">
-        <v>-466.9150205904238</v>
+        <v>-479.4377378419072</v>
       </c>
       <c r="D91">
-        <v>339.8789794095762</v>
+        <v>337.2022621580928</v>
       </c>
       <c r="E91">
-        <v>803.394</v>
+        <v>813.24</v>
       </c>
       <c r="F91">
-        <v>876.294</v>
+        <v>886.14</v>
       </c>
       <c r="G91">
         <v>69.5</v>
@@ -8737,37 +8737,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M91">
-        <v>175.9598352</v>
+        <v>177.936912</v>
       </c>
       <c r="N91">
-        <v>-85.05983520000001</v>
+        <v>-87.036912</v>
       </c>
       <c r="O91">
-        <v>-10.6324794</v>
+        <v>-10.879614</v>
       </c>
       <c r="P91">
-        <v>-74.42735580000002</v>
+        <v>-76.157298</v>
       </c>
       <c r="Q91">
-        <v>-73.92735580000002</v>
+        <v>-75.657298</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4984419856886042</v>
+        <v>0.5437061842574645</v>
       </c>
       <c r="T91">
-        <v>7.632194153967597</v>
+        <v>8.395413569364356</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.06457439555501471</v>
+        <v>0.0638569022710701</v>
       </c>
       <c r="W91">
-        <v>0.1878334613725531</v>
+        <v>0.1879775340239691</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5165951644401177</v>
+        <v>0.5108552181685608</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2235503990473187</v>
+        <v>0.2251003990473187</v>
       </c>
       <c r="C92">
-        <v>-479.4377378419072</v>
+        <v>-491.9186235587575</v>
       </c>
       <c r="D92">
-        <v>337.2022621580928</v>
+        <v>334.5673764412426</v>
       </c>
       <c r="E92">
-        <v>813.24</v>
+        <v>823.0860000000001</v>
       </c>
       <c r="F92">
-        <v>886.14</v>
+        <v>895.9860000000001</v>
       </c>
       <c r="G92">
         <v>69.5</v>
@@ -8819,37 +8819,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M92">
-        <v>177.936912</v>
+        <v>179.9139888</v>
       </c>
       <c r="N92">
-        <v>-87.036912</v>
+        <v>-89.01398880000002</v>
       </c>
       <c r="O92">
-        <v>-10.879614</v>
+        <v>-11.1267486</v>
       </c>
       <c r="P92">
-        <v>-76.157298</v>
+        <v>-77.88724020000002</v>
       </c>
       <c r="Q92">
-        <v>-75.657298</v>
+        <v>-77.38724020000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5437061842574645</v>
+        <v>0.5990290936194052</v>
       </c>
       <c r="T92">
-        <v>8.395413569364356</v>
+        <v>9.328237299293731</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.0638569022710701</v>
+        <v>0.0631551780702891</v>
       </c>
       <c r="W92">
-        <v>0.1879775340239691</v>
+        <v>0.188118440243486</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5108552181685608</v>
+        <v>0.5052414245623128</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2251003990473187</v>
+        <v>0.2593010367212384</v>
       </c>
       <c r="C93">
-        <v>-491.9186235587575</v>
+        <v>-550.9658825304405</v>
       </c>
       <c r="D93">
-        <v>334.5673764412426</v>
+        <v>285.3661174695597</v>
       </c>
       <c r="E93">
-        <v>823.0860000000001</v>
+        <v>832.9320000000001</v>
       </c>
       <c r="F93">
-        <v>895.9860000000001</v>
+        <v>905.8320000000001</v>
       </c>
       <c r="G93">
         <v>69.5</v>
@@ -8901,45 +8901,45 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M93">
-        <v>179.9139888</v>
+        <v>213.5951856</v>
       </c>
       <c r="N93">
-        <v>-89.01398880000002</v>
+        <v>-122.6951856</v>
       </c>
       <c r="O93">
-        <v>-11.1267486</v>
+        <v>-15.3368982</v>
       </c>
       <c r="P93">
-        <v>-77.88724020000002</v>
+        <v>-107.3582874</v>
       </c>
       <c r="Q93">
-        <v>-77.38724020000002</v>
+        <v>-106.8582874</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5990290936194052</v>
+        <v>0.673815701245828</v>
       </c>
       <c r="T93">
-        <v>9.328237299293731</v>
+        <v>10.58924694393179</v>
       </c>
       <c r="U93">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0631551780702891</v>
+        <v>0.05319642373062925</v>
       </c>
       <c r="W93">
-        <v>0.188118440243486</v>
+        <v>0.2232562832843176</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.5052414245623128</v>
+        <v>0.425571389845034</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2593010367212384</v>
+        <v>0.2612010367212385</v>
       </c>
       <c r="C94">
-        <v>-550.9658825304405</v>
+        <v>-563.1243771987392</v>
       </c>
       <c r="D94">
-        <v>285.3661174695597</v>
+        <v>283.0536228012609</v>
       </c>
       <c r="E94">
-        <v>832.9320000000001</v>
+        <v>842.7780000000001</v>
       </c>
       <c r="F94">
-        <v>905.8320000000001</v>
+        <v>915.6780000000001</v>
       </c>
       <c r="G94">
         <v>69.5</v>
@@ -8983,37 +8983,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M94">
-        <v>213.5951856</v>
+        <v>215.9168724</v>
       </c>
       <c r="N94">
-        <v>-122.6951856</v>
+        <v>-125.0168724</v>
       </c>
       <c r="O94">
-        <v>-15.3368982</v>
+        <v>-15.62710905</v>
       </c>
       <c r="P94">
-        <v>-107.3582874</v>
+        <v>-109.38976335</v>
       </c>
       <c r="Q94">
-        <v>-106.8582874</v>
+        <v>-108.88976335</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.673815701245828</v>
+        <v>0.7635322299952323</v>
       </c>
       <c r="T94">
-        <v>10.58924694393179</v>
+        <v>12.10199650735062</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05319642373062925</v>
+        <v>0.05262441917438592</v>
       </c>
       <c r="W94">
-        <v>0.2232562832843176</v>
+        <v>0.2233911619586798</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.425571389845034</v>
+        <v>0.4209953533950874</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2612010367212385</v>
+        <v>0.2631010367212385</v>
       </c>
       <c r="C95">
-        <v>-563.1243771987392</v>
+        <v>-575.2456940487</v>
       </c>
       <c r="D95">
-        <v>283.0536228012609</v>
+        <v>280.7783059513002</v>
       </c>
       <c r="E95">
-        <v>842.7780000000001</v>
+        <v>852.6240000000001</v>
       </c>
       <c r="F95">
-        <v>915.6780000000001</v>
+        <v>925.5240000000001</v>
       </c>
       <c r="G95">
         <v>69.5</v>
@@ -9065,37 +9065,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M95">
-        <v>215.9168724</v>
+        <v>218.2385592</v>
       </c>
       <c r="N95">
-        <v>-125.0168724</v>
+        <v>-127.3385592</v>
       </c>
       <c r="O95">
-        <v>-15.62710905</v>
+        <v>-15.9173199</v>
       </c>
       <c r="P95">
-        <v>-109.38976335</v>
+        <v>-111.4212393</v>
       </c>
       <c r="Q95">
-        <v>-108.88976335</v>
+        <v>-110.9212393</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7635322299952323</v>
+        <v>0.8831542683277711</v>
       </c>
       <c r="T95">
-        <v>12.10199650735062</v>
+        <v>14.1189959252424</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05262441917438592</v>
+        <v>0.05206458492784991</v>
       </c>
       <c r="W95">
-        <v>0.2233911619586798</v>
+        <v>0.223523170874013</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4209953533950874</v>
+        <v>0.4165166794227992</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2631010367212385</v>
+        <v>0.2650010367212385</v>
       </c>
       <c r="C96">
-        <v>-575.2456940487</v>
+        <v>-587.330722488701</v>
       </c>
       <c r="D96">
-        <v>280.7783059513002</v>
+        <v>278.5392775112991</v>
       </c>
       <c r="E96">
-        <v>852.6240000000001</v>
+        <v>862.4700000000001</v>
       </c>
       <c r="F96">
-        <v>925.5240000000001</v>
+        <v>935.3700000000001</v>
       </c>
       <c r="G96">
         <v>69.5</v>
@@ -9147,37 +9147,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M96">
-        <v>218.2385592</v>
+        <v>220.560246</v>
       </c>
       <c r="N96">
-        <v>-127.3385592</v>
+        <v>-129.660246</v>
       </c>
       <c r="O96">
-        <v>-15.9173199</v>
+        <v>-16.20753075</v>
       </c>
       <c r="P96">
-        <v>-111.4212393</v>
+        <v>-113.45271525</v>
       </c>
       <c r="Q96">
-        <v>-110.9212393</v>
+        <v>-112.95271525</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8831542683277711</v>
+        <v>1.050625121993326</v>
       </c>
       <c r="T96">
-        <v>14.1189959252424</v>
+        <v>16.94279511029088</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05206458492784991</v>
+        <v>0.05151653666545148</v>
       </c>
       <c r="W96">
-        <v>0.223523170874013</v>
+        <v>0.2236524006542865</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4165166794227992</v>
+        <v>0.4121322933236119</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2650010367212385</v>
+        <v>0.2669010367212384</v>
       </c>
       <c r="C97">
-        <v>-587.330722488701</v>
+        <v>-599.3803237816976</v>
       </c>
       <c r="D97">
-        <v>278.5392775112991</v>
+        <v>276.3356762183026</v>
       </c>
       <c r="E97">
-        <v>862.4700000000001</v>
+        <v>872.3160000000001</v>
       </c>
       <c r="F97">
-        <v>935.3700000000001</v>
+        <v>945.2160000000001</v>
       </c>
       <c r="G97">
         <v>69.5</v>
@@ -9229,37 +9229,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M97">
-        <v>220.560246</v>
+        <v>222.8819328</v>
       </c>
       <c r="N97">
-        <v>-129.660246</v>
+        <v>-131.9819328</v>
       </c>
       <c r="O97">
-        <v>-16.20753075</v>
+        <v>-16.4977416</v>
       </c>
       <c r="P97">
-        <v>-113.45271525</v>
+        <v>-115.4841912</v>
       </c>
       <c r="Q97">
-        <v>-112.95271525</v>
+        <v>-114.9841912</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.050625121993326</v>
+        <v>1.301831402491658</v>
       </c>
       <c r="T97">
-        <v>16.94279511029088</v>
+        <v>21.17849388786361</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05151653666545148</v>
+        <v>0.05097990607518636</v>
       </c>
       <c r="W97">
-        <v>0.2236524006542865</v>
+        <v>0.2237789381474711</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4121322933236119</v>
+        <v>0.4078392486014909</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2669010367212384</v>
+        <v>0.2688010367212385</v>
       </c>
       <c r="C98">
-        <v>-599.3803237816974</v>
+        <v>-611.3953321498143</v>
       </c>
       <c r="D98">
-        <v>276.3356762183026</v>
+        <v>274.1666678501857</v>
       </c>
       <c r="E98">
-        <v>872.316</v>
+        <v>882.162</v>
       </c>
       <c r="F98">
-        <v>945.216</v>
+        <v>955.062</v>
       </c>
       <c r="G98">
         <v>69.5</v>
@@ -9311,37 +9311,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M98">
-        <v>222.8819328</v>
+        <v>225.2036196</v>
       </c>
       <c r="N98">
-        <v>-131.9819328</v>
+        <v>-134.3036196</v>
       </c>
       <c r="O98">
-        <v>-16.4977416</v>
+        <v>-16.78795245</v>
       </c>
       <c r="P98">
-        <v>-115.4841912</v>
+        <v>-117.51566715</v>
       </c>
       <c r="Q98">
-        <v>-114.9841912</v>
+        <v>-117.01566715</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.301831402491655</v>
+        <v>1.72050853665554</v>
       </c>
       <c r="T98">
-        <v>21.17849388786356</v>
+        <v>28.23799185048475</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05097990607518637</v>
+        <v>0.05045434003317414</v>
       </c>
       <c r="W98">
-        <v>0.2237789381474711</v>
+        <v>0.2239028666201775</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4078392486014909</v>
+        <v>0.403634720265393</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2688010367212385</v>
+        <v>0.2707010367212384</v>
       </c>
       <c r="C99">
-        <v>-611.3953321498143</v>
+        <v>-623.3765558273221</v>
       </c>
       <c r="D99">
-        <v>274.1666678501857</v>
+        <v>272.0314441726779</v>
       </c>
       <c r="E99">
-        <v>882.162</v>
+        <v>892.008</v>
       </c>
       <c r="F99">
-        <v>955.062</v>
+        <v>964.908</v>
       </c>
       <c r="G99">
         <v>69.5</v>
@@ -9393,37 +9393,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M99">
-        <v>225.2036196</v>
+        <v>227.5253064</v>
       </c>
       <c r="N99">
-        <v>-134.3036196</v>
+        <v>-136.6253064</v>
       </c>
       <c r="O99">
-        <v>-16.78795245</v>
+        <v>-17.0781633</v>
       </c>
       <c r="P99">
-        <v>-117.51566715</v>
+        <v>-119.5471431</v>
       </c>
       <c r="Q99">
-        <v>-117.01566715</v>
+        <v>-119.0471431</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.72050853665554</v>
+        <v>2.557862804983309</v>
       </c>
       <c r="T99">
-        <v>28.23799185048475</v>
+        <v>42.35698777572711</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05045434003317414</v>
+        <v>0.04993949982875399</v>
       </c>
       <c r="W99">
-        <v>0.2239028666201775</v>
+        <v>0.2240242659403798</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.403634720265393</v>
+        <v>0.399515998630032</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2707010367212384</v>
+        <v>0.2726010367212385</v>
       </c>
       <c r="C100">
-        <v>-623.3765558273221</v>
+        <v>-635.3247780647908</v>
       </c>
       <c r="D100">
-        <v>272.0314441726779</v>
+        <v>269.9292219352092</v>
       </c>
       <c r="E100">
-        <v>892.008</v>
+        <v>901.854</v>
       </c>
       <c r="F100">
-        <v>964.908</v>
+        <v>974.754</v>
       </c>
       <c r="G100">
         <v>69.5</v>
@@ -9475,37 +9475,37 @@
         <v>90.90000000000001</v>
       </c>
       <c r="M100">
-        <v>227.5253064</v>
+        <v>229.8469932</v>
       </c>
       <c r="N100">
-        <v>-136.6253064</v>
+        <v>-138.9469932</v>
       </c>
       <c r="O100">
-        <v>-17.0781633</v>
+        <v>-17.36837415</v>
       </c>
       <c r="P100">
-        <v>-119.5471431</v>
+        <v>-121.57861905</v>
       </c>
       <c r="Q100">
-        <v>-119.0471431</v>
+        <v>-121.07861905</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.557862804983309</v>
+        <v>5.069925609966618</v>
       </c>
       <c r="T100">
-        <v>42.35698777572711</v>
+        <v>84.71397555145423</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04993949982875399</v>
+        <v>0.04943506043654436</v>
       </c>
       <c r="W100">
-        <v>0.2240242659403798</v>
+        <v>0.2241432127490628</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.399515998630032</v>
+        <v>0.3954804834923549</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2726010367212385</v>
-      </c>
-      <c r="C101">
-        <v>-635.3247780647908</v>
-      </c>
-      <c r="D101">
-        <v>269.9292219352092</v>
-      </c>
-      <c r="E101">
-        <v>901.854</v>
-      </c>
-      <c r="F101">
-        <v>974.754</v>
-      </c>
-      <c r="G101">
-        <v>69.5</v>
-      </c>
-      <c r="H101">
-        <v>911.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="K101">
-        <v>0.5</v>
-      </c>
-      <c r="L101">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="M101">
-        <v>229.8469932</v>
-      </c>
-      <c r="N101">
-        <v>-138.9469932</v>
-      </c>
-      <c r="O101">
-        <v>-17.36837415</v>
-      </c>
-      <c r="P101">
-        <v>-121.57861905</v>
-      </c>
-      <c r="Q101">
-        <v>-121.07861905</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.069925609966618</v>
-      </c>
-      <c r="T101">
-        <v>84.71397555145423</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04943506043654436</v>
-      </c>
-      <c r="W101">
-        <v>0.2241432127490628</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3954804834923549</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
